--- a/GTM 资料.xlsx
+++ b/GTM 资料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12240\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF517AAA-2813-4379-A892-090D6438EE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393FA0A4-693C-4771-8E36-7EAEEB08400F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7323,7 +7323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7401,9 +7401,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7798,7 +7795,7 @@
       <c r="B2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="16" t="s">
@@ -7833,7 +7830,7 @@
       <c r="B3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="16" t="s">
@@ -7868,7 +7865,7 @@
       <c r="B4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="16" t="s">
@@ -7903,7 +7900,7 @@
       <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="16" t="s">
@@ -7938,7 +7935,7 @@
       <c r="B6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="16" t="s">
@@ -7973,7 +7970,7 @@
       <c r="B7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="16" t="s">
@@ -8008,7 +8005,7 @@
       <c r="B8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="16" t="s">
@@ -8043,7 +8040,7 @@
       <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D9" s="16" t="s">
@@ -8078,7 +8075,7 @@
       <c r="B10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D10" s="16" t="s">
@@ -8113,7 +8110,7 @@
       <c r="B11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -8148,7 +8145,7 @@
       <c r="B12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="16" t="s">
@@ -8183,7 +8180,7 @@
       <c r="B13" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="16" t="s">
@@ -8218,7 +8215,7 @@
       <c r="B14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="16" t="s">
@@ -8253,7 +8250,7 @@
       <c r="B15" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D15" s="16" t="s">
@@ -8288,7 +8285,7 @@
       <c r="B16" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="16" t="s">
@@ -8323,7 +8320,7 @@
       <c r="B17" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="16" t="s">
@@ -8358,7 +8355,7 @@
       <c r="B18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="16" t="s">
@@ -8393,7 +8390,7 @@
       <c r="B19" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="16" t="s">
@@ -8428,7 +8425,7 @@
       <c r="B20" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="16" t="s">
@@ -8463,7 +8460,7 @@
       <c r="B21" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="16" t="s">
@@ -8498,7 +8495,7 @@
       <c r="B22" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="16" t="s">
@@ -8533,7 +8530,7 @@
       <c r="B23" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="16" t="s">
@@ -8568,7 +8565,7 @@
       <c r="B24" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="16" t="s">
@@ -8603,7 +8600,7 @@
       <c r="B25" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="16" t="s">
@@ -8638,7 +8635,7 @@
       <c r="B26" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="16" t="s">
@@ -8673,7 +8670,7 @@
       <c r="B27" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="16" t="s">
@@ -8708,7 +8705,7 @@
       <c r="B28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="16" t="s">
@@ -8743,7 +8740,7 @@
       <c r="B29" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="16" t="s">
@@ -8778,7 +8775,7 @@
       <c r="B30" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="16" t="s">
@@ -8813,7 +8810,7 @@
       <c r="B31" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="16" t="s">
@@ -8848,7 +8845,7 @@
       <c r="B32" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D32" s="16" t="s">
@@ -8883,7 +8880,7 @@
       <c r="B33" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D33" s="16" t="s">
@@ -8918,7 +8915,7 @@
       <c r="B34" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="16" t="s">
@@ -8953,7 +8950,7 @@
       <c r="B35" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="16" t="s">
@@ -8988,7 +8985,7 @@
       <c r="B36" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="16" t="s">
@@ -9023,7 +9020,7 @@
       <c r="B37" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="16" t="s">
@@ -9058,7 +9055,7 @@
       <c r="B38" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="16" t="s">
@@ -9093,7 +9090,7 @@
       <c r="B39" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="16" t="s">
@@ -9128,7 +9125,7 @@
       <c r="B40" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="16" t="s">
@@ -9163,7 +9160,7 @@
       <c r="B41" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="16" t="s">
@@ -9198,7 +9195,7 @@
       <c r="B42" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D42" s="16" t="s">
@@ -9233,7 +9230,7 @@
       <c r="B43" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D43" s="16" t="s">
@@ -9268,7 +9265,7 @@
       <c r="B44" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D44" s="16" t="s">
@@ -9303,7 +9300,7 @@
       <c r="B45" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D45" s="16" t="s">
@@ -9338,7 +9335,7 @@
       <c r="B46" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="16" t="s">
@@ -9373,7 +9370,7 @@
       <c r="B47" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="16" t="s">
@@ -9408,7 +9405,7 @@
       <c r="B48" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="16" t="s">
@@ -9443,7 +9440,7 @@
       <c r="B49" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D49" s="16" t="s">
@@ -9478,7 +9475,7 @@
       <c r="B50" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D50" s="16" t="s">
@@ -9513,7 +9510,7 @@
       <c r="B51" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D51" s="16" t="s">
@@ -9548,7 +9545,7 @@
       <c r="B52" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="16" t="s">
@@ -9583,7 +9580,7 @@
       <c r="B53" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D53" s="16" t="s">
@@ -9618,7 +9615,7 @@
       <c r="B54" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D54" s="16" t="s">
@@ -9653,7 +9650,7 @@
       <c r="B55" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D55" s="16" t="s">
@@ -9688,7 +9685,7 @@
       <c r="B56" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="26" t="s">
+      <c r="C56" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D56" s="16" t="s">
@@ -9723,7 +9720,7 @@
       <c r="B57" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D57" s="16" t="s">
@@ -9758,7 +9755,7 @@
       <c r="B58" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="26" t="s">
+      <c r="C58" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D58" s="16" t="s">
@@ -9793,7 +9790,7 @@
       <c r="B59" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D59" s="16" t="s">
@@ -9828,7 +9825,7 @@
       <c r="B60" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C60" s="26" t="s">
+      <c r="C60" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D60" s="16" t="s">
@@ -9863,7 +9860,7 @@
       <c r="B61" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D61" s="16" t="s">
@@ -9898,7 +9895,7 @@
       <c r="B62" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C62" s="26" t="s">
+      <c r="C62" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D62" s="16" t="s">
@@ -9933,7 +9930,7 @@
       <c r="B63" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D63" s="16" t="s">
@@ -9968,7 +9965,7 @@
       <c r="B64" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C64" s="26" t="s">
+      <c r="C64" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D64" s="16" t="s">
@@ -10003,7 +10000,7 @@
       <c r="B65" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D65" s="16" t="s">
@@ -10038,7 +10035,7 @@
       <c r="B66" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="26" t="s">
+      <c r="C66" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="16" t="s">
@@ -10073,7 +10070,7 @@
       <c r="B67" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D67" s="16" t="s">
@@ -10108,7 +10105,7 @@
       <c r="B68" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C68" s="26" t="s">
+      <c r="C68" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D68" s="16" t="s">
@@ -10143,7 +10140,7 @@
       <c r="B69" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D69" s="16" t="s">
@@ -10178,7 +10175,7 @@
       <c r="B70" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C70" s="26" t="s">
+      <c r="C70" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D70" s="16" t="s">
@@ -10213,7 +10210,7 @@
       <c r="B71" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D71" s="16" t="s">
@@ -10248,7 +10245,7 @@
       <c r="B72" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D72" s="16" t="s">
@@ -10283,7 +10280,7 @@
       <c r="B73" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D73" s="16" t="s">
@@ -10318,7 +10315,7 @@
       <c r="B74" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D74" s="16" t="s">
@@ -10353,7 +10350,7 @@
       <c r="B75" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D75" s="16" t="s">
@@ -10388,7 +10385,7 @@
       <c r="B76" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D76" s="16" t="s">
@@ -10423,7 +10420,7 @@
       <c r="B77" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C77" s="26" t="s">
+      <c r="C77" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D77" s="16" t="s">
@@ -10458,7 +10455,7 @@
       <c r="B78" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C78" s="26" t="s">
+      <c r="C78" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D78" s="16" t="s">
@@ -10493,7 +10490,7 @@
       <c r="B79" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D79" s="16" t="s">
@@ -10528,7 +10525,7 @@
       <c r="B80" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C80" s="26" t="s">
+      <c r="C80" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D80" s="16" t="s">
@@ -10563,7 +10560,7 @@
       <c r="B81" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C81" s="26" t="s">
+      <c r="C81" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D81" s="16" t="s">
@@ -10598,7 +10595,7 @@
       <c r="B82" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C82" s="26" t="s">
+      <c r="C82" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D82" s="16" t="s">
@@ -10633,7 +10630,7 @@
       <c r="B83" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C83" s="26" t="s">
+      <c r="C83" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D83" s="16" t="s">
@@ -10668,7 +10665,7 @@
       <c r="B84" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C84" s="26" t="s">
+      <c r="C84" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D84" s="16" t="s">
@@ -10703,7 +10700,7 @@
       <c r="B85" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C85" s="26" t="s">
+      <c r="C85" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D85" s="16" t="s">
@@ -10738,7 +10735,7 @@
       <c r="B86" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C86" s="26" t="s">
+      <c r="C86" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D86" s="16" t="s">
@@ -10773,7 +10770,7 @@
       <c r="B87" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C87" s="26" t="s">
+      <c r="C87" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D87" s="16" t="s">
@@ -10808,7 +10805,7 @@
       <c r="B88" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C88" s="26" t="s">
+      <c r="C88" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="16" t="s">
@@ -10843,7 +10840,7 @@
       <c r="B89" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C89" s="26" t="s">
+      <c r="C89" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D89" s="16" t="s">
@@ -10878,7 +10875,7 @@
       <c r="B90" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C90" s="26" t="s">
+      <c r="C90" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D90" s="16" t="s">
@@ -10913,7 +10910,7 @@
       <c r="B91" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C91" s="26" t="s">
+      <c r="C91" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D91" s="16" t="s">
@@ -10948,7 +10945,7 @@
       <c r="B92" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C92" s="26" t="s">
+      <c r="C92" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D92" s="16" t="s">
@@ -10983,7 +10980,7 @@
       <c r="B93" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C93" s="26" t="s">
+      <c r="C93" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D93" s="16" t="s">
@@ -11018,7 +11015,7 @@
       <c r="B94" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C94" s="26" t="s">
+      <c r="C94" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D94" s="16" t="s">
@@ -11053,7 +11050,7 @@
       <c r="B95" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C95" s="26" t="s">
+      <c r="C95" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D95" s="16" t="s">
@@ -11088,7 +11085,7 @@
       <c r="B96" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C96" s="26" t="s">
+      <c r="C96" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D96" s="16" t="s">
@@ -11123,7 +11120,7 @@
       <c r="B97" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C97" s="26" t="s">
+      <c r="C97" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D97" s="16" t="s">
@@ -11158,7 +11155,7 @@
       <c r="B98" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="26" t="s">
+      <c r="C98" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D98" s="16" t="s">
@@ -11193,7 +11190,7 @@
       <c r="B99" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C99" s="26" t="s">
+      <c r="C99" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="16" t="s">
@@ -11228,7 +11225,7 @@
       <c r="B100" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C100" s="26" t="s">
+      <c r="C100" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="16" t="s">
@@ -11263,7 +11260,7 @@
       <c r="B101" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C101" s="26" t="s">
+      <c r="C101" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="16" t="s">
@@ -11298,7 +11295,7 @@
       <c r="B102" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C102" s="26" t="s">
+      <c r="C102" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D102" s="16" t="s">
@@ -11333,7 +11330,7 @@
       <c r="B103" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C103" s="26" t="s">
+      <c r="C103" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D103" s="16" t="s">
@@ -11368,7 +11365,7 @@
       <c r="B104" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C104" s="26" t="s">
+      <c r="C104" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D104" s="16" t="s">
@@ -11403,7 +11400,7 @@
       <c r="B105" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C105" s="26" t="s">
+      <c r="C105" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D105" s="16" t="s">
@@ -11438,7 +11435,7 @@
       <c r="B106" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C106" s="26" t="s">
+      <c r="C106" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D106" s="16" t="s">
@@ -11473,7 +11470,7 @@
       <c r="B107" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C107" s="26" t="s">
+      <c r="C107" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D107" s="16" t="s">
@@ -11508,7 +11505,7 @@
       <c r="B108" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C108" s="26" t="s">
+      <c r="C108" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D108" s="16" t="s">
@@ -11543,7 +11540,7 @@
       <c r="B109" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="26" t="s">
+      <c r="C109" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D109" s="16" t="s">
@@ -11578,7 +11575,7 @@
       <c r="B110" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="26" t="s">
+      <c r="C110" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D110" s="16" t="s">
@@ -11613,7 +11610,7 @@
       <c r="B111" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C111" s="26" t="s">
+      <c r="C111" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D111" s="16" t="s">
@@ -11648,7 +11645,7 @@
       <c r="B112" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C112" s="26" t="s">
+      <c r="C112" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D112" s="16" t="s">
@@ -11683,7 +11680,7 @@
       <c r="B113" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="26" t="s">
+      <c r="C113" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D113" s="16" t="s">
@@ -11718,7 +11715,7 @@
       <c r="B114" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C114" s="26" t="s">
+      <c r="C114" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D114" s="16" t="s">
@@ -11753,7 +11750,7 @@
       <c r="B115" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="26" t="s">
+      <c r="C115" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D115" s="16" t="s">
@@ -11788,7 +11785,7 @@
       <c r="B116" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C116" s="26" t="s">
+      <c r="C116" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D116" s="16" t="s">
@@ -11823,7 +11820,7 @@
       <c r="B117" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C117" s="26" t="s">
+      <c r="C117" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D117" s="16" t="s">
@@ -11858,7 +11855,7 @@
       <c r="B118" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C118" s="26" t="s">
+      <c r="C118" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D118" s="16" t="s">
@@ -11893,7 +11890,7 @@
       <c r="B119" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C119" s="26" t="s">
+      <c r="C119" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D119" s="16" t="s">
@@ -11928,7 +11925,7 @@
       <c r="B120" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C120" s="26" t="s">
+      <c r="C120" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="16" t="s">
@@ -11963,7 +11960,7 @@
       <c r="B121" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C121" s="26" t="s">
+      <c r="C121" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="16" t="s">
@@ -11998,7 +11995,7 @@
       <c r="B122" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C122" s="26" t="s">
+      <c r="C122" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D122" s="16" t="s">
@@ -12033,7 +12030,7 @@
       <c r="B123" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C123" s="26" t="s">
+      <c r="C123" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D123" s="16" t="s">
@@ -12068,7 +12065,7 @@
       <c r="B124" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C124" s="26" t="s">
+      <c r="C124" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D124" s="16" t="s">
@@ -12103,7 +12100,7 @@
       <c r="B125" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C125" s="26" t="s">
+      <c r="C125" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D125" s="16" t="s">
@@ -12138,7 +12135,7 @@
       <c r="B126" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C126" s="26" t="s">
+      <c r="C126" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D126" s="16" t="s">
@@ -12173,7 +12170,7 @@
       <c r="B127" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C127" s="26" t="s">
+      <c r="C127" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D127" s="16" t="s">
@@ -12208,7 +12205,7 @@
       <c r="B128" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C128" s="26" t="s">
+      <c r="C128" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D128" s="16" t="s">
@@ -12243,7 +12240,7 @@
       <c r="B129" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C129" s="26" t="s">
+      <c r="C129" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D129" s="16" t="s">
@@ -12278,7 +12275,7 @@
       <c r="B130" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C130" s="26" t="s">
+      <c r="C130" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D130" s="16" t="s">
@@ -12313,7 +12310,7 @@
       <c r="B131" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C131" s="26" t="s">
+      <c r="C131" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D131" s="16" t="s">
@@ -12348,7 +12345,7 @@
       <c r="B132" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C132" s="26" t="s">
+      <c r="C132" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D132" s="16" t="s">
@@ -12383,7 +12380,7 @@
       <c r="B133" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C133" s="26" t="s">
+      <c r="C133" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D133" s="16" t="s">
@@ -12418,7 +12415,7 @@
       <c r="B134" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C134" s="26" t="s">
+      <c r="C134" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="16" t="s">
@@ -12453,7 +12450,7 @@
       <c r="B135" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C135" s="26" t="s">
+      <c r="C135" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D135" s="16" t="s">
@@ -12488,7 +12485,7 @@
       <c r="B136" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C136" s="26" t="s">
+      <c r="C136" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D136" s="16" t="s">
@@ -12523,7 +12520,7 @@
       <c r="B137" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C137" s="26" t="s">
+      <c r="C137" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="16" t="s">
@@ -12558,7 +12555,7 @@
       <c r="B138" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="26" t="s">
+      <c r="C138" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D138" s="16" t="s">
@@ -12593,7 +12590,7 @@
       <c r="B139" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C139" s="26" t="s">
+      <c r="C139" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D139" s="16" t="s">
@@ -12628,7 +12625,7 @@
       <c r="B140" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C140" s="26" t="s">
+      <c r="C140" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D140" s="16" t="s">
@@ -12663,7 +12660,7 @@
       <c r="B141" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C141" s="26" t="s">
+      <c r="C141" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D141" s="16" t="s">
@@ -12698,7 +12695,7 @@
       <c r="B142" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C142" s="26" t="s">
+      <c r="C142" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D142" s="16" t="s">
@@ -12733,7 +12730,7 @@
       <c r="B143" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C143" s="26" t="s">
+      <c r="C143" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D143" s="16" t="s">
@@ -12768,7 +12765,7 @@
       <c r="B144" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C144" s="26" t="s">
+      <c r="C144" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D144" s="16" t="s">
@@ -12803,7 +12800,7 @@
       <c r="B145" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C145" s="26" t="s">
+      <c r="C145" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D145" s="16" t="s">
@@ -12838,7 +12835,7 @@
       <c r="B146" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C146" s="26" t="s">
+      <c r="C146" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D146" s="16" t="s">
@@ -12873,7 +12870,7 @@
       <c r="B147" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C147" s="26" t="s">
+      <c r="C147" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D147" s="16" t="s">
@@ -12908,7 +12905,7 @@
       <c r="B148" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C148" s="26" t="s">
+      <c r="C148" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="16" t="s">
@@ -12943,7 +12940,7 @@
       <c r="B149" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="C149" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D149" s="16" t="s">
@@ -12978,7 +12975,7 @@
       <c r="B150" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="C150" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D150" s="16" t="s">
@@ -13013,7 +13010,7 @@
       <c r="B151" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C151" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D151" s="16" t="s">
@@ -13048,7 +13045,7 @@
       <c r="B152" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="C152" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D152" s="16" t="s">
@@ -13083,7 +13080,7 @@
       <c r="B153" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="C153" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D153" s="16" t="s">
@@ -13118,7 +13115,7 @@
       <c r="B154" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="C154" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D154" s="16" t="s">
@@ -13153,7 +13150,7 @@
       <c r="B155" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C155" s="26" t="s">
+      <c r="C155" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D155" s="16" t="s">
@@ -13188,7 +13185,7 @@
       <c r="B156" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C156" s="26" t="s">
+      <c r="C156" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D156" s="16" t="s">
@@ -13223,7 +13220,7 @@
       <c r="B157" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C157" s="26" t="s">
+      <c r="C157" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D157" s="16" t="s">
@@ -13258,7 +13255,7 @@
       <c r="B158" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C158" s="26" t="s">
+      <c r="C158" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D158" s="16" t="s">
@@ -13293,7 +13290,7 @@
       <c r="B159" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C159" s="26" t="s">
+      <c r="C159" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D159" s="16" t="s">
@@ -13328,7 +13325,7 @@
       <c r="B160" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C160" s="26" t="s">
+      <c r="C160" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D160" s="16" t="s">
@@ -13363,7 +13360,7 @@
       <c r="B161" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C161" s="26" t="s">
+      <c r="C161" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D161" s="16" t="s">
@@ -13398,7 +13395,7 @@
       <c r="B162" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C162" s="26" t="s">
+      <c r="C162" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="16" t="s">
@@ -13433,7 +13430,7 @@
       <c r="B163" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C163" s="26" t="s">
+      <c r="C163" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D163" s="16" t="s">
@@ -13468,7 +13465,7 @@
       <c r="B164" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C164" s="26" t="s">
+      <c r="C164" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D164" s="16" t="s">
@@ -13503,7 +13500,7 @@
       <c r="B165" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C165" s="26" t="s">
+      <c r="C165" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D165" s="16" t="s">
@@ -13538,7 +13535,7 @@
       <c r="B166" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C166" s="26" t="s">
+      <c r="C166" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D166" s="16" t="s">
@@ -13573,7 +13570,7 @@
       <c r="B167" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C167" s="26" t="s">
+      <c r="C167" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D167" s="16" t="s">
@@ -13606,7 +13603,7 @@
       <c r="B168" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C168" s="26" t="s">
+      <c r="C168" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D168" s="16" t="s">
@@ -13641,7 +13638,7 @@
       <c r="B169" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C169" s="26" t="s">
+      <c r="C169" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D169" s="16" t="s">
@@ -13676,7 +13673,7 @@
       <c r="B170" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C170" s="26" t="s">
+      <c r="C170" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D170" s="16" t="s">
@@ -13711,7 +13708,7 @@
       <c r="B171" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C171" s="26" t="s">
+      <c r="C171" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D171" s="16" t="s">
@@ -13746,7 +13743,7 @@
       <c r="B172" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C172" s="26" t="s">
+      <c r="C172" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D172" s="16" t="s">
@@ -13781,7 +13778,7 @@
       <c r="B173" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C173" s="26" t="s">
+      <c r="C173" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D173" s="16" t="s">
@@ -13816,7 +13813,7 @@
       <c r="B174" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C174" s="26" t="s">
+      <c r="C174" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D174" s="16" t="s">
@@ -13851,7 +13848,7 @@
       <c r="B175" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D175" s="16" t="s">
@@ -13886,7 +13883,7 @@
       <c r="B176" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C176" s="26" t="s">
+      <c r="C176" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="16" t="s">
@@ -13921,7 +13918,7 @@
       <c r="B177" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C177" s="26" t="s">
+      <c r="C177" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D177" s="16" t="s">
@@ -13956,7 +13953,7 @@
       <c r="B178" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C178" s="26" t="s">
+      <c r="C178" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D178" s="16" t="s">
@@ -13991,7 +13988,7 @@
       <c r="B179" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C179" s="26" t="s">
+      <c r="C179" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D179" s="16" t="s">
@@ -14026,7 +14023,7 @@
       <c r="B180" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C180" s="26" t="s">
+      <c r="C180" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D180" s="16" t="s">
@@ -14061,7 +14058,7 @@
       <c r="B181" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C181" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D181" s="16" t="s">
@@ -14096,7 +14093,7 @@
       <c r="B182" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C182" s="26" t="s">
+      <c r="C182" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D182" s="16" t="s">
@@ -14131,7 +14128,7 @@
       <c r="B183" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C183" s="26" t="s">
+      <c r="C183" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D183" s="16" t="s">
@@ -14166,7 +14163,7 @@
       <c r="B184" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C184" s="26" t="s">
+      <c r="C184" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D184" s="16" t="s">
@@ -14201,7 +14198,7 @@
       <c r="B185" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C185" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D185" s="16" t="s">
@@ -14236,7 +14233,7 @@
       <c r="B186" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C186" s="26" t="s">
+      <c r="C186" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D186" s="16" t="s">
@@ -14271,7 +14268,7 @@
       <c r="B187" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C187" s="26" t="s">
+      <c r="C187" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D187" s="16" t="s">
@@ -14306,7 +14303,7 @@
       <c r="B188" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C188" s="26" t="s">
+      <c r="C188" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D188" s="16" t="s">
@@ -14341,7 +14338,7 @@
       <c r="B189" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C189" s="26" t="s">
+      <c r="C189" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D189" s="16" t="s">
@@ -14376,7 +14373,7 @@
       <c r="B190" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C190" s="26" t="s">
+      <c r="C190" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D190" s="16" t="s">
@@ -14411,7 +14408,7 @@
       <c r="B191" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C191" s="26" t="s">
+      <c r="C191" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D191" s="16" t="s">
@@ -14446,7 +14443,7 @@
       <c r="B192" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C192" s="26" t="s">
+      <c r="C192" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D192" s="16" t="s">
@@ -14481,7 +14478,7 @@
       <c r="B193" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C193" s="26" t="s">
+      <c r="C193" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D193" s="16" t="s">
@@ -14516,7 +14513,7 @@
       <c r="B194" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C194" s="26" t="s">
+      <c r="C194" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D194" s="16" t="s">
@@ -14551,7 +14548,7 @@
       <c r="B195" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C195" s="26" t="s">
+      <c r="C195" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D195" s="16" t="s">
@@ -14586,7 +14583,7 @@
       <c r="B196" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C196" s="26" t="s">
+      <c r="C196" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D196" s="16" t="s">
@@ -14621,7 +14618,7 @@
       <c r="B197" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C197" s="26" t="s">
+      <c r="C197" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D197" s="16" t="s">
@@ -14656,7 +14653,7 @@
       <c r="B198" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C198" s="26" t="s">
+      <c r="C198" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D198" s="16" t="s">
@@ -14691,7 +14688,7 @@
       <c r="B199" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C199" s="26" t="s">
+      <c r="C199" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D199" s="16" t="s">
@@ -14726,7 +14723,7 @@
       <c r="B200" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C200" s="26" t="s">
+      <c r="C200" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D200" s="16" t="s">
@@ -14761,7 +14758,7 @@
       <c r="B201" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C201" s="26" t="s">
+      <c r="C201" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D201" s="16" t="s">
@@ -14796,7 +14793,7 @@
       <c r="B202" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C202" s="26" t="s">
+      <c r="C202" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D202" s="16" t="s">
@@ -14831,7 +14828,7 @@
       <c r="B203" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C203" s="26" t="s">
+      <c r="C203" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D203" s="16" t="s">
@@ -14866,7 +14863,7 @@
       <c r="B204" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C204" s="26" t="s">
+      <c r="C204" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D204" s="16" t="s">
@@ -14901,7 +14898,7 @@
       <c r="B205" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C205" s="26" t="s">
+      <c r="C205" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D205" s="16" t="s">
@@ -14936,7 +14933,7 @@
       <c r="B206" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C206" s="26" t="s">
+      <c r="C206" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D206" s="16" t="s">
@@ -14971,7 +14968,7 @@
       <c r="B207" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C207" s="26" t="s">
+      <c r="C207" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D207" s="16" t="s">
@@ -15006,7 +15003,7 @@
       <c r="B208" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C208" s="26" t="s">
+      <c r="C208" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D208" s="16" t="s">
@@ -15041,7 +15038,7 @@
       <c r="B209" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C209" s="26" t="s">
+      <c r="C209" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D209" s="16" t="s">
@@ -15076,7 +15073,7 @@
       <c r="B210" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C210" s="26" t="s">
+      <c r="C210" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D210" s="16" t="s">
@@ -15111,7 +15108,7 @@
       <c r="B211" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C211" s="26" t="s">
+      <c r="C211" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D211" s="16" t="s">
@@ -15146,7 +15143,7 @@
       <c r="B212" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C212" s="26" t="s">
+      <c r="C212" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D212" s="16" t="s">
@@ -15181,7 +15178,7 @@
       <c r="B213" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C213" s="26" t="s">
+      <c r="C213" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D213" s="16" t="s">
@@ -15216,7 +15213,7 @@
       <c r="B214" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C214" s="26" t="s">
+      <c r="C214" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D214" s="16" t="s">
@@ -15251,7 +15248,7 @@
       <c r="B215" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C215" s="26" t="s">
+      <c r="C215" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D215" s="16" t="s">
@@ -15286,7 +15283,7 @@
       <c r="B216" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C216" s="26" t="s">
+      <c r="C216" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D216" s="16" t="s">
@@ -15321,7 +15318,7 @@
       <c r="B217" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C217" s="26" t="s">
+      <c r="C217" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D217" s="16" t="s">
@@ -15356,7 +15353,7 @@
       <c r="B218" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C218" s="26" t="s">
+      <c r="C218" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D218" s="16" t="s">
@@ -15391,7 +15388,7 @@
       <c r="B219" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C219" s="26" t="s">
+      <c r="C219" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D219" s="16" t="s">
@@ -15426,7 +15423,7 @@
       <c r="B220" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C220" s="26" t="s">
+      <c r="C220" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D220" s="16" t="s">
@@ -15461,7 +15458,7 @@
       <c r="B221" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C221" s="26" t="s">
+      <c r="C221" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D221" s="16" t="s">
@@ -15496,7 +15493,7 @@
       <c r="B222" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C222" s="26" t="s">
+      <c r="C222" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D222" s="16" t="s">
@@ -15531,7 +15528,7 @@
       <c r="B223" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C223" s="26" t="s">
+      <c r="C223" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D223" s="16" t="s">
@@ -15566,7 +15563,7 @@
       <c r="B224" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C224" s="26" t="s">
+      <c r="C224" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D224" s="16" t="s">
@@ -15601,7 +15598,7 @@
       <c r="B225" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C225" s="26" t="s">
+      <c r="C225" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D225" s="16" t="s">
@@ -15636,7 +15633,7 @@
       <c r="B226" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C226" s="26" t="s">
+      <c r="C226" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D226" s="16" t="s">
@@ -15671,7 +15668,7 @@
       <c r="B227" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C227" s="26" t="s">
+      <c r="C227" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D227" s="16" t="s">
@@ -15706,7 +15703,7 @@
       <c r="B228" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C228" s="26" t="s">
+      <c r="C228" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D228" s="16" t="s">
@@ -15741,7 +15738,7 @@
       <c r="B229" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C229" s="26" t="s">
+      <c r="C229" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D229" s="16" t="s">
@@ -15776,7 +15773,7 @@
       <c r="B230" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C230" s="26" t="s">
+      <c r="C230" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D230" s="16" t="s">
@@ -15811,7 +15808,7 @@
       <c r="B231" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C231" s="26" t="s">
+      <c r="C231" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D231" s="16" t="s">
@@ -15846,7 +15843,7 @@
       <c r="B232" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C232" s="26" t="s">
+      <c r="C232" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D232" s="16" t="s">
@@ -15874,14 +15871,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A233" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B233" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C233" s="26" t="s">
+      <c r="C233" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D233" s="16" t="s">
@@ -15909,14 +15906,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A234" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B234" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C234" s="26" t="s">
+      <c r="C234" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D234" s="16" t="s">
@@ -15944,14 +15941,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A235" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B235" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C235" s="26" t="s">
+      <c r="C235" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D235" s="16" t="s">
@@ -15979,14 +15976,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A236" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B236" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C236" s="26" t="s">
+      <c r="C236" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D236" s="16" t="s">
@@ -16014,14 +16011,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A237" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B237" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C237" s="26" t="s">
+      <c r="C237" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D237" s="16" t="s">
@@ -16049,14 +16046,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A238" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B238" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C238" s="26" t="s">
+      <c r="C238" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D238" s="16" t="s">
@@ -16084,14 +16081,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A239" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B239" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C239" s="26" t="s">
+      <c r="C239" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D239" s="16" t="s">
@@ -16119,14 +16116,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A240" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B240" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C240" s="26" t="s">
+      <c r="C240" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D240" s="16" t="s">
@@ -16154,14 +16151,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A241" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B241" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C241" s="26" t="s">
+      <c r="C241" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D241" s="16" t="s">
@@ -16189,14 +16186,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A242" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B242" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C242" s="26" t="s">
+      <c r="C242" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D242" s="16" t="s">
@@ -16224,14 +16221,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A243" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B243" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C243" s="26" t="s">
+      <c r="C243" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D243" s="16" t="s">
@@ -16259,14 +16256,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A244" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B244" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C244" s="26" t="s">
+      <c r="C244" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D244" s="16" t="s">
@@ -16294,14 +16291,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A245" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B245" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C245" s="26" t="s">
+      <c r="C245" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D245" s="16" t="s">
@@ -16329,14 +16326,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A246" s="16" t="s">
         <v>1584</v>
       </c>
       <c r="B246" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C246" s="26" t="s">
+      <c r="C246" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D246" s="16" t="s">
@@ -16371,7 +16368,7 @@
       <c r="B247" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C247" s="26" t="s">
+      <c r="C247" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D247" s="16" t="s">
@@ -16406,7 +16403,7 @@
       <c r="B248" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C248" s="26" t="s">
+      <c r="C248" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D248" s="16" t="s">
@@ -16441,7 +16438,7 @@
       <c r="B249" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C249" s="26" t="s">
+      <c r="C249" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D249" s="16" t="s">
@@ -16476,7 +16473,7 @@
       <c r="B250" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C250" s="26" t="s">
+      <c r="C250" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D250" s="16" t="s">
@@ -16511,7 +16508,7 @@
       <c r="B251" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C251" s="26" t="s">
+      <c r="C251" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D251" s="16" t="s">
@@ -16546,7 +16543,7 @@
       <c r="B252" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C252" s="26" t="s">
+      <c r="C252" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D252" s="16" t="s">
@@ -16581,7 +16578,7 @@
       <c r="B253" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C253" s="26" t="s">
+      <c r="C253" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D253" s="16" t="s">
@@ -16616,7 +16613,7 @@
       <c r="B254" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C254" s="26" t="s">
+      <c r="C254" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D254" s="16" t="s">
@@ -16651,7 +16648,7 @@
       <c r="B255" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C255" s="26" t="s">
+      <c r="C255" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D255" s="16" t="s">
@@ -16686,7 +16683,7 @@
       <c r="B256" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C256" s="26" t="s">
+      <c r="C256" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D256" s="16" t="s">
@@ -16721,7 +16718,7 @@
       <c r="B257" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C257" s="26" t="s">
+      <c r="C257" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D257" s="16" t="s">
@@ -16756,7 +16753,7 @@
       <c r="B258" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C258" s="26" t="s">
+      <c r="C258" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D258" s="16" t="s">
@@ -16791,7 +16788,7 @@
       <c r="B259" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C259" s="26" t="s">
+      <c r="C259" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D259" s="16" t="s">
@@ -16826,7 +16823,7 @@
       <c r="B260" s="16" t="s">
         <v>2056</v>
       </c>
-      <c r="C260" s="26" t="s">
+      <c r="C260" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D260" s="16" t="s">
@@ -16861,7 +16858,7 @@
       <c r="B261" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C261" s="26" t="s">
+      <c r="C261" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D261" s="16" t="s">
@@ -16896,7 +16893,7 @@
       <c r="B262" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C262" s="26" t="s">
+      <c r="C262" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D262" s="16" t="s">
@@ -16931,7 +16928,7 @@
       <c r="B263" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C263" s="26" t="s">
+      <c r="C263" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D263" s="16" t="s">
@@ -16966,7 +16963,7 @@
       <c r="B264" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C264" s="26" t="s">
+      <c r="C264" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D264" s="16" t="s">
@@ -17001,7 +16998,7 @@
       <c r="B265" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C265" s="26" t="s">
+      <c r="C265" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D265" s="16" t="s">
@@ -17036,7 +17033,7 @@
       <c r="B266" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C266" s="26" t="s">
+      <c r="C266" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D266" s="16" t="s">
@@ -17071,7 +17068,7 @@
       <c r="B267" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C267" s="26" t="s">
+      <c r="C267" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D267" s="16" t="s">
@@ -17106,7 +17103,7 @@
       <c r="B268" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C268" s="26" t="s">
+      <c r="C268" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D268" s="16" t="s">
@@ -17141,7 +17138,7 @@
       <c r="B269" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C269" s="26" t="s">
+      <c r="C269" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D269" s="16" t="s">
@@ -17176,7 +17173,7 @@
       <c r="B270" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C270" s="26" t="s">
+      <c r="C270" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D270" s="16" t="s">
@@ -17211,7 +17208,7 @@
       <c r="B271" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C271" s="26" t="s">
+      <c r="C271" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D271" s="16" t="s">
@@ -17246,7 +17243,7 @@
       <c r="B272" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C272" s="26" t="s">
+      <c r="C272" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D272" s="16" t="s">
@@ -17281,7 +17278,7 @@
       <c r="B273" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C273" s="26" t="s">
+      <c r="C273" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D273" s="16" t="s">
@@ -17316,7 +17313,7 @@
       <c r="B274" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C274" s="26" t="s">
+      <c r="C274" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D274" s="16" t="s">
@@ -17351,7 +17348,7 @@
       <c r="B275" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C275" s="26" t="s">
+      <c r="C275" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D275" s="16" t="s">
@@ -17386,7 +17383,7 @@
       <c r="B276" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C276" s="26" t="s">
+      <c r="C276" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D276" s="16" t="s">
@@ -17421,7 +17418,7 @@
       <c r="B277" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C277" s="26" t="s">
+      <c r="C277" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D277" s="16" t="s">
@@ -17456,7 +17453,7 @@
       <c r="B278" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C278" s="26" t="s">
+      <c r="C278" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D278" s="16" t="s">
@@ -17491,7 +17488,7 @@
       <c r="B279" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C279" s="26" t="s">
+      <c r="C279" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D279" s="16" t="s">
@@ -17526,7 +17523,7 @@
       <c r="B280" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C280" s="26" t="s">
+      <c r="C280" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D280" s="16" t="s">
@@ -17561,7 +17558,7 @@
       <c r="B281" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C281" s="26" t="s">
+      <c r="C281" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D281" s="16" t="s">
@@ -17596,7 +17593,7 @@
       <c r="B282" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C282" s="26" t="s">
+      <c r="C282" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D282" s="16" t="s">
@@ -17631,7 +17628,7 @@
       <c r="B283" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C283" s="26" t="s">
+      <c r="C283" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D283" s="16" t="s">
@@ -17666,7 +17663,7 @@
       <c r="B284" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C284" s="26" t="s">
+      <c r="C284" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D284" s="16" t="s">
@@ -17701,7 +17698,7 @@
       <c r="B285" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C285" s="26" t="s">
+      <c r="C285" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D285" s="16" t="s">
@@ -17736,7 +17733,7 @@
       <c r="B286" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C286" s="26" t="s">
+      <c r="C286" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D286" s="16" t="s">
@@ -17771,7 +17768,7 @@
       <c r="B287" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C287" s="26" t="s">
+      <c r="C287" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D287" s="16" t="s">
@@ -17806,7 +17803,7 @@
       <c r="B288" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C288" s="26" t="s">
+      <c r="C288" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D288" s="16" t="s">
@@ -17841,7 +17838,7 @@
       <c r="B289" s="16" t="s">
         <v>2060</v>
       </c>
-      <c r="C289" s="26" t="s">
+      <c r="C289" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D289" s="16" t="s">
@@ -17876,7 +17873,7 @@
       <c r="B290" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C290" s="26" t="s">
+      <c r="C290" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D290" s="16" t="s">
@@ -17911,7 +17908,7 @@
       <c r="B291" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C291" s="26" t="s">
+      <c r="C291" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D291" s="16" t="s">
@@ -17946,7 +17943,7 @@
       <c r="B292" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C292" s="26" t="s">
+      <c r="C292" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D292" s="16" t="s">
@@ -17981,7 +17978,7 @@
       <c r="B293" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C293" s="26" t="s">
+      <c r="C293" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D293" s="16" t="s">
@@ -18016,7 +18013,7 @@
       <c r="B294" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C294" s="26" t="s">
+      <c r="C294" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D294" s="16" t="s">
@@ -18051,7 +18048,7 @@
       <c r="B295" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C295" s="26" t="s">
+      <c r="C295" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D295" s="16" t="s">
@@ -18086,7 +18083,7 @@
       <c r="B296" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C296" s="26" t="s">
+      <c r="C296" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D296" s="16" t="s">
@@ -18121,7 +18118,7 @@
       <c r="B297" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C297" s="26" t="s">
+      <c r="C297" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D297" s="16" t="s">
@@ -18156,7 +18153,7 @@
       <c r="B298" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C298" s="26" t="s">
+      <c r="C298" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D298" s="16" t="s">
@@ -18191,7 +18188,7 @@
       <c r="B299" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C299" s="26" t="s">
+      <c r="C299" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D299" s="16" t="s">
@@ -18226,7 +18223,7 @@
       <c r="B300" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C300" s="26" t="s">
+      <c r="C300" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D300" s="16" t="s">
@@ -18261,7 +18258,7 @@
       <c r="B301" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C301" s="26" t="s">
+      <c r="C301" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D301" s="16" t="s">
@@ -18296,7 +18293,7 @@
       <c r="B302" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C302" s="26" t="s">
+      <c r="C302" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D302" s="16" t="s">
@@ -18331,7 +18328,7 @@
       <c r="B303" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="C303" s="26" t="s">
+      <c r="C303" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D303" s="16" t="s">
@@ -18366,7 +18363,7 @@
       <c r="B304" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C304" s="26" t="s">
+      <c r="C304" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D304" s="16" t="s">
@@ -18401,7 +18398,7 @@
       <c r="B305" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C305" s="26" t="s">
+      <c r="C305" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D305" s="16" t="s">
@@ -18436,7 +18433,7 @@
       <c r="B306" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C306" s="26" t="s">
+      <c r="C306" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D306" s="16" t="s">
@@ -18471,7 +18468,7 @@
       <c r="B307" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C307" s="26" t="s">
+      <c r="C307" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D307" s="16" t="s">
@@ -18506,7 +18503,7 @@
       <c r="B308" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C308" s="26" t="s">
+      <c r="C308" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D308" s="16" t="s">
@@ -18541,7 +18538,7 @@
       <c r="B309" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C309" s="26" t="s">
+      <c r="C309" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D309" s="16" t="s">
@@ -18576,7 +18573,7 @@
       <c r="B310" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C310" s="26" t="s">
+      <c r="C310" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D310" s="16" t="s">
@@ -18611,7 +18608,7 @@
       <c r="B311" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C311" s="26" t="s">
+      <c r="C311" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D311" s="16" t="s">
@@ -18646,7 +18643,7 @@
       <c r="B312" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C312" s="26" t="s">
+      <c r="C312" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D312" s="16" t="s">
@@ -18681,7 +18678,7 @@
       <c r="B313" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C313" s="26" t="s">
+      <c r="C313" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D313" s="16" t="s">
@@ -18716,7 +18713,7 @@
       <c r="B314" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C314" s="26" t="s">
+      <c r="C314" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D314" s="16" t="s">
@@ -18751,7 +18748,7 @@
       <c r="B315" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C315" s="26" t="s">
+      <c r="C315" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D315" s="16" t="s">
@@ -18786,7 +18783,7 @@
       <c r="B316" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C316" s="26" t="s">
+      <c r="C316" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D316" s="16" t="s">
@@ -18821,7 +18818,7 @@
       <c r="B317" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C317" s="26" t="s">
+      <c r="C317" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D317" s="16" t="s">
@@ -18856,7 +18853,7 @@
       <c r="B318" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C318" s="26" t="s">
+      <c r="C318" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D318" s="17" t="s">
@@ -18891,7 +18888,7 @@
       <c r="B319" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C319" s="26" t="s">
+      <c r="C319" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D319" s="17" t="s">
@@ -18926,7 +18923,7 @@
       <c r="B320" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C320" s="26" t="s">
+      <c r="C320" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D320" s="17" t="s">
@@ -18961,7 +18958,7 @@
       <c r="B321" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C321" s="26" t="s">
+      <c r="C321" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D321" s="17" t="s">
@@ -18996,7 +18993,7 @@
       <c r="B322" s="20" t="s">
         <v>2075</v>
       </c>
-      <c r="C322" s="26" t="s">
+      <c r="C322" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D322" s="16" t="s">
@@ -19031,7 +19028,7 @@
       <c r="B323" s="20" t="s">
         <v>2075</v>
       </c>
-      <c r="C323" s="26" t="s">
+      <c r="C323" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D323" s="16" t="s">
@@ -19066,7 +19063,7 @@
       <c r="B324" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="C324" s="26" t="s">
+      <c r="C324" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D324" s="16" t="s">
@@ -19101,7 +19098,7 @@
       <c r="B325" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C325" s="26" t="s">
+      <c r="C325" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D325" s="16" t="s">
@@ -19136,7 +19133,7 @@
       <c r="B326" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C326" s="26" t="s">
+      <c r="C326" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D326" s="16" t="s">
@@ -19171,7 +19168,7 @@
       <c r="B327" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C327" s="26" t="s">
+      <c r="C327" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D327" s="16" t="s">
@@ -19206,7 +19203,7 @@
       <c r="B328" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C328" s="26" t="s">
+      <c r="C328" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D328" s="16" t="s">
@@ -19241,7 +19238,7 @@
       <c r="B329" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C329" s="26" t="s">
+      <c r="C329" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D329" s="16" t="s">
@@ -19276,7 +19273,7 @@
       <c r="B330" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C330" s="26" t="s">
+      <c r="C330" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D330" s="16" t="s">
@@ -19311,7 +19308,7 @@
       <c r="B331" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C331" s="26" t="s">
+      <c r="C331" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D331" s="16" t="s">
@@ -19346,7 +19343,7 @@
       <c r="B332" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C332" s="26" t="s">
+      <c r="C332" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D332" s="16" t="s">
@@ -19381,7 +19378,7 @@
       <c r="B333" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C333" s="26" t="s">
+      <c r="C333" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D333" s="16" t="s">
@@ -19416,7 +19413,7 @@
       <c r="B334" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C334" s="26" t="s">
+      <c r="C334" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D334" s="16" t="s">
@@ -19451,7 +19448,7 @@
       <c r="B335" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C335" s="26" t="s">
+      <c r="C335" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D335" s="16" t="s">
@@ -19486,7 +19483,7 @@
       <c r="B336" s="20" t="s">
         <v>2077</v>
       </c>
-      <c r="C336" s="26" t="s">
+      <c r="C336" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D336" s="16" t="s">
@@ -19521,7 +19518,7 @@
       <c r="B337" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C337" s="26" t="s">
+      <c r="C337" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D337" s="16" t="s">
@@ -19556,7 +19553,7 @@
       <c r="B338" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C338" s="26" t="s">
+      <c r="C338" s="16" t="s">
         <v>2084</v>
       </c>
       <c r="D338" s="16" t="s">
@@ -19591,7 +19588,7 @@
       <c r="B339" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C339" s="26" t="s">
+      <c r="C339" s="16" t="s">
         <v>2084</v>
       </c>
       <c r="D339" s="16" t="s">
@@ -19626,7 +19623,7 @@
       <c r="B340" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C340" s="26" t="s">
+      <c r="C340" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D340" s="16" t="s">
@@ -19661,7 +19658,7 @@
       <c r="B341" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C341" s="26" t="s">
+      <c r="C341" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D341" s="16" t="s">
@@ -19696,7 +19693,7 @@
       <c r="B342" s="20" t="s">
         <v>2078</v>
       </c>
-      <c r="C342" s="26" t="s">
+      <c r="C342" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D342" s="16" t="s">
@@ -19731,7 +19728,7 @@
       <c r="B343" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C343" s="26" t="s">
+      <c r="C343" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D343" s="16" t="s">
@@ -19766,7 +19763,7 @@
       <c r="B344" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C344" s="26" t="s">
+      <c r="C344" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D344" s="16" t="s">
@@ -19801,7 +19798,7 @@
       <c r="B345" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C345" s="26" t="s">
+      <c r="C345" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D345" s="16" t="s">
@@ -19836,7 +19833,7 @@
       <c r="B346" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C346" s="26" t="s">
+      <c r="C346" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D346" s="16" t="s">
@@ -19871,7 +19868,7 @@
       <c r="B347" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C347" s="26" t="s">
+      <c r="C347" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D347" s="16" t="s">
@@ -19906,7 +19903,7 @@
       <c r="B348" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C348" s="26" t="s">
+      <c r="C348" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D348" s="16" t="s">
@@ -19941,7 +19938,7 @@
       <c r="B349" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C349" s="26" t="s">
+      <c r="C349" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D349" s="16" t="s">
@@ -19976,7 +19973,7 @@
       <c r="B350" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C350" s="26" t="s">
+      <c r="C350" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D350" s="16" t="s">
@@ -20011,7 +20008,7 @@
       <c r="B351" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C351" s="26" t="s">
+      <c r="C351" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D351" s="16" t="s">
@@ -20046,7 +20043,7 @@
       <c r="B352" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C352" s="26" t="s">
+      <c r="C352" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D352" s="16" t="s">
@@ -20081,7 +20078,7 @@
       <c r="B353" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C353" s="26" t="s">
+      <c r="C353" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D353" s="16" t="s">
@@ -20116,7 +20113,7 @@
       <c r="B354" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C354" s="26" t="s">
+      <c r="C354" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D354" s="16" t="s">
@@ -20151,7 +20148,7 @@
       <c r="B355" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C355" s="26" t="s">
+      <c r="C355" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D355" s="16" t="s">
@@ -20186,7 +20183,7 @@
       <c r="B356" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C356" s="26" t="s">
+      <c r="C356" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D356" s="16" t="s">
@@ -20221,7 +20218,7 @@
       <c r="B357" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C357" s="26" t="s">
+      <c r="C357" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D357" s="16" t="s">
@@ -20256,7 +20253,7 @@
       <c r="B358" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C358" s="26" t="s">
+      <c r="C358" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D358" s="16" t="s">
@@ -20291,7 +20288,7 @@
       <c r="B359" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C359" s="26" t="s">
+      <c r="C359" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D359" s="16" t="s">
@@ -20326,7 +20323,7 @@
       <c r="B360" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C360" s="26" t="s">
+      <c r="C360" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D360" s="16" t="s">
@@ -20361,7 +20358,7 @@
       <c r="B361" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C361" s="26" t="s">
+      <c r="C361" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D361" s="16" t="s">
@@ -20396,7 +20393,7 @@
       <c r="B362" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C362" s="26" t="s">
+      <c r="C362" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D362" s="16" t="s">
@@ -20431,7 +20428,7 @@
       <c r="B363" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C363" s="26" t="s">
+      <c r="C363" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D363" s="16" t="s">
@@ -20466,7 +20463,7 @@
       <c r="B364" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C364" s="26" t="s">
+      <c r="C364" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D364" s="16" t="s">
@@ -20501,7 +20498,7 @@
       <c r="B365" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C365" s="26" t="s">
+      <c r="C365" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D365" s="16" t="s">
@@ -20536,7 +20533,7 @@
       <c r="B366" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C366" s="26" t="s">
+      <c r="C366" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D366" s="16" t="s">
@@ -20571,7 +20568,7 @@
       <c r="B367" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C367" s="26" t="s">
+      <c r="C367" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D367" s="16" t="s">
@@ -20606,7 +20603,7 @@
       <c r="B368" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C368" s="26" t="s">
+      <c r="C368" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D368" s="16" t="s">
@@ -20641,7 +20638,7 @@
       <c r="B369" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C369" s="26" t="s">
+      <c r="C369" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D369" s="16" t="s">
@@ -20676,7 +20673,7 @@
       <c r="B370" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C370" s="26" t="s">
+      <c r="C370" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D370" s="16" t="s">
@@ -20711,7 +20708,7 @@
       <c r="B371" s="16" t="s">
         <v>2092</v>
       </c>
-      <c r="C371" s="26" t="s">
+      <c r="C371" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D371" s="16" t="s">
@@ -20746,7 +20743,7 @@
       <c r="B372" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C372" s="26" t="s">
+      <c r="C372" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D372" s="16" t="s">
@@ -20781,7 +20778,7 @@
       <c r="B373" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C373" s="26" t="s">
+      <c r="C373" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D373" s="16" t="s">
@@ -20816,7 +20813,7 @@
       <c r="B374" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C374" s="26" t="s">
+      <c r="C374" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D374" s="16" t="s">
@@ -20851,7 +20848,7 @@
       <c r="B375" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C375" s="26" t="s">
+      <c r="C375" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D375" s="16" t="s">
@@ -20886,7 +20883,7 @@
       <c r="B376" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C376" s="26" t="s">
+      <c r="C376" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D376" s="16" t="s">
@@ -20921,7 +20918,7 @@
       <c r="B377" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C377" s="26" t="s">
+      <c r="C377" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D377" s="16" t="s">
@@ -20956,7 +20953,7 @@
       <c r="B378" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C378" s="26" t="s">
+      <c r="C378" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D378" s="16" t="s">
@@ -20991,7 +20988,7 @@
       <c r="B379" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C379" s="26" t="s">
+      <c r="C379" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D379" s="16" t="s">
@@ -21026,7 +21023,7 @@
       <c r="B380" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C380" s="26" t="s">
+      <c r="C380" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D380" s="16" t="s">
@@ -21061,7 +21058,7 @@
       <c r="B381" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C381" s="26" t="s">
+      <c r="C381" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D381" s="16" t="s">
@@ -21096,7 +21093,7 @@
       <c r="B382" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C382" s="26" t="s">
+      <c r="C382" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D382" s="16" t="s">
@@ -21131,7 +21128,7 @@
       <c r="B383" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C383" s="26" t="s">
+      <c r="C383" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D383" s="16" t="s">
@@ -21166,7 +21163,7 @@
       <c r="B384" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C384" s="26" t="s">
+      <c r="C384" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D384" s="16" t="s">
@@ -21201,7 +21198,7 @@
       <c r="B385" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C385" s="26" t="s">
+      <c r="C385" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D385" s="16" t="s">
@@ -21236,7 +21233,7 @@
       <c r="B386" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C386" s="26" t="s">
+      <c r="C386" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D386" s="16" t="s">
@@ -21271,7 +21268,7 @@
       <c r="B387" s="16" t="s">
         <v>2090</v>
       </c>
-      <c r="C387" s="26" t="s">
+      <c r="C387" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D387" s="16" t="s">
@@ -21306,7 +21303,7 @@
       <c r="B388" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C388" s="26" t="s">
+      <c r="C388" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D388" s="16" t="s">
@@ -21341,7 +21338,7 @@
       <c r="B389" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C389" s="26" t="s">
+      <c r="C389" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D389" s="16" t="s">
@@ -21376,7 +21373,7 @@
       <c r="B390" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C390" s="26" t="s">
+      <c r="C390" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D390" s="16" t="s">
@@ -21411,7 +21408,7 @@
       <c r="B391" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C391" s="26" t="s">
+      <c r="C391" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D391" s="16" t="s">
@@ -21446,7 +21443,7 @@
       <c r="B392" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C392" s="26" t="s">
+      <c r="C392" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D392" s="16" t="s">
@@ -21481,7 +21478,7 @@
       <c r="B393" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C393" s="26" t="s">
+      <c r="C393" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D393" s="16" t="s">
@@ -21516,7 +21513,7 @@
       <c r="B394" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C394" s="26" t="s">
+      <c r="C394" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D394" s="16" t="s">
@@ -21551,7 +21548,7 @@
       <c r="B395" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C395" s="26" t="s">
+      <c r="C395" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D395" s="16" t="s">
@@ -21586,7 +21583,7 @@
       <c r="B396" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C396" s="26" t="s">
+      <c r="C396" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D396" s="16" t="s">
@@ -21621,7 +21618,7 @@
       <c r="B397" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C397" s="26" t="s">
+      <c r="C397" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D397" s="16" t="s">
@@ -21656,7 +21653,7 @@
       <c r="B398" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C398" s="26" t="s">
+      <c r="C398" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D398" s="16" t="s">
@@ -21691,7 +21688,7 @@
       <c r="B399" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C399" s="26" t="s">
+      <c r="C399" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D399" s="16" t="s">
@@ -21726,7 +21723,7 @@
       <c r="B400" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C400" s="26" t="s">
+      <c r="C400" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D400" s="16" t="s">
@@ -21761,7 +21758,7 @@
       <c r="B401" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C401" s="26" t="s">
+      <c r="C401" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D401" s="16" t="s">
@@ -21796,7 +21793,7 @@
       <c r="B402" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C402" s="26" t="s">
+      <c r="C402" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D402" s="16" t="s">
@@ -21831,7 +21828,7 @@
       <c r="B403" s="16" t="s">
         <v>2091</v>
       </c>
-      <c r="C403" s="26" t="s">
+      <c r="C403" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D403" s="16" t="s">
@@ -21866,7 +21863,7 @@
       <c r="B404" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C404" s="26" t="s">
+      <c r="C404" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D404" s="16" t="s">
@@ -21901,7 +21898,7 @@
       <c r="B405" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C405" s="26" t="s">
+      <c r="C405" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D405" s="16" t="s">
@@ -21936,7 +21933,7 @@
       <c r="B406" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C406" s="26" t="s">
+      <c r="C406" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D406" s="16" t="s">
@@ -21971,7 +21968,7 @@
       <c r="B407" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C407" s="26" t="s">
+      <c r="C407" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D407" s="16" t="s">
@@ -22006,7 +22003,7 @@
       <c r="B408" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C408" s="26" t="s">
+      <c r="C408" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D408" s="16" t="s">
@@ -22041,7 +22038,7 @@
       <c r="B409" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C409" s="26" t="s">
+      <c r="C409" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D409" s="16" t="s">
@@ -22076,7 +22073,7 @@
       <c r="B410" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C410" s="26" t="s">
+      <c r="C410" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D410" s="16" t="s">
@@ -22111,7 +22108,7 @@
       <c r="B411" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C411" s="26" t="s">
+      <c r="C411" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D411" s="16" t="s">
@@ -22146,7 +22143,7 @@
       <c r="B412" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C412" s="26" t="s">
+      <c r="C412" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D412" s="16" t="s">
@@ -22181,7 +22178,7 @@
       <c r="B413" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C413" s="26" t="s">
+      <c r="C413" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D413" s="16" t="s">
@@ -22216,7 +22213,7 @@
       <c r="B414" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C414" s="26" t="s">
+      <c r="C414" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D414" s="16" t="s">
@@ -22251,7 +22248,7 @@
       <c r="B415" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C415" s="26" t="s">
+      <c r="C415" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D415" s="16" t="s">
@@ -22286,7 +22283,7 @@
       <c r="B416" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C416" s="26" t="s">
+      <c r="C416" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D416" s="16" t="s">
@@ -22321,7 +22318,7 @@
       <c r="B417" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C417" s="26" t="s">
+      <c r="C417" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D417" s="16" t="s">
@@ -22356,7 +22353,7 @@
       <c r="B418" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="C418" s="26" t="s">
+      <c r="C418" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D418" s="16" t="s">
@@ -22391,7 +22388,7 @@
       <c r="B419" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C419" s="26" t="s">
+      <c r="C419" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D419" s="16" t="s">
@@ -22426,7 +22423,7 @@
       <c r="B420" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C420" s="26" t="s">
+      <c r="C420" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D420" s="16" t="s">
@@ -22461,7 +22458,7 @@
       <c r="B421" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C421" s="26" t="s">
+      <c r="C421" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D421" s="16" t="s">
@@ -22496,7 +22493,7 @@
       <c r="B422" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C422" s="26" t="s">
+      <c r="C422" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D422" s="16" t="s">
@@ -22531,7 +22528,7 @@
       <c r="B423" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C423" s="26" t="s">
+      <c r="C423" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D423" s="16" t="s">
@@ -22566,7 +22563,7 @@
       <c r="B424" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C424" s="26" t="s">
+      <c r="C424" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D424" s="16" t="s">
@@ -22601,7 +22598,7 @@
       <c r="B425" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C425" s="26" t="s">
+      <c r="C425" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D425" s="16" t="s">
@@ -22636,7 +22633,7 @@
       <c r="B426" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C426" s="26" t="s">
+      <c r="C426" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D426" s="16" t="s">
@@ -22671,7 +22668,7 @@
       <c r="B427" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C427" s="26" t="s">
+      <c r="C427" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D427" s="16" t="s">
@@ -22706,7 +22703,7 @@
       <c r="B428" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C428" s="26" t="s">
+      <c r="C428" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D428" s="16" t="s">
@@ -22741,7 +22738,7 @@
       <c r="B429" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C429" s="26" t="s">
+      <c r="C429" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D429" s="16" t="s">
@@ -22776,7 +22773,7 @@
       <c r="B430" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C430" s="26" t="s">
+      <c r="C430" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D430" s="16" t="s">
@@ -22811,7 +22808,7 @@
       <c r="B431" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C431" s="26" t="s">
+      <c r="C431" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D431" s="16" t="s">
@@ -22846,7 +22843,7 @@
       <c r="B432" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C432" s="26" t="s">
+      <c r="C432" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D432" s="16" t="s">
@@ -22881,7 +22878,7 @@
       <c r="B433" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C433" s="26" t="s">
+      <c r="C433" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D433" s="16" t="s">
@@ -22916,7 +22913,7 @@
       <c r="B434" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C434" s="26" t="s">
+      <c r="C434" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D434" s="16" t="s">
@@ -22951,7 +22948,7 @@
       <c r="B435" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C435" s="26" t="s">
+      <c r="C435" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D435" s="16" t="s">
@@ -22986,7 +22983,7 @@
       <c r="B436" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="C436" s="26" t="s">
+      <c r="C436" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D436" s="16" t="s">
@@ -23021,7 +23018,7 @@
       <c r="B437" s="16" t="s">
         <v>2099</v>
       </c>
-      <c r="C437" s="26" t="s">
+      <c r="C437" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D437" s="16" t="s">
@@ -23056,7 +23053,7 @@
       <c r="B438" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C438" s="26" t="s">
+      <c r="C438" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D438" s="16" t="s">
@@ -23091,7 +23088,7 @@
       <c r="B439" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C439" s="26" t="s">
+      <c r="C439" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D439" s="16" t="s">
@@ -23126,7 +23123,7 @@
       <c r="B440" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C440" s="26" t="s">
+      <c r="C440" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D440" s="16" t="s">
@@ -23161,7 +23158,7 @@
       <c r="B441" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C441" s="26" t="s">
+      <c r="C441" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D441" s="16" t="s">
@@ -23196,7 +23193,7 @@
       <c r="B442" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C442" s="26" t="s">
+      <c r="C442" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D442" s="16" t="s">
@@ -23231,7 +23228,7 @@
       <c r="B443" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C443" s="26" t="s">
+      <c r="C443" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D443" s="16" t="s">
@@ -23266,7 +23263,7 @@
       <c r="B444" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C444" s="26" t="s">
+      <c r="C444" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D444" s="16" t="s">
@@ -23301,7 +23298,7 @@
       <c r="B445" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C445" s="26" t="s">
+      <c r="C445" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D445" s="16" t="s">
@@ -23336,7 +23333,7 @@
       <c r="B446" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C446" s="26" t="s">
+      <c r="C446" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D446" s="16" t="s">
@@ -23371,7 +23368,7 @@
       <c r="B447" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C447" s="26" t="s">
+      <c r="C447" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D447" s="16" t="s">
@@ -23406,7 +23403,7 @@
       <c r="B448" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C448" s="26" t="s">
+      <c r="C448" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D448" s="16" t="s">
@@ -23441,7 +23438,7 @@
       <c r="B449" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C449" s="26" t="s">
+      <c r="C449" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D449" s="16" t="s">
@@ -23476,7 +23473,7 @@
       <c r="B450" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="C450" s="26" t="s">
+      <c r="C450" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D450" s="16" t="s">
@@ -23511,7 +23508,7 @@
       <c r="B451" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C451" s="26" t="s">
+      <c r="C451" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D451" s="16" t="s">
@@ -23546,7 +23543,7 @@
       <c r="B452" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C452" s="26" t="s">
+      <c r="C452" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D452" s="16" t="s">
@@ -23581,7 +23578,7 @@
       <c r="B453" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C453" s="26" t="s">
+      <c r="C453" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D453" s="16" t="s">
@@ -23616,7 +23613,7 @@
       <c r="B454" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C454" s="26" t="s">
+      <c r="C454" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D454" s="16" t="s">
@@ -23651,7 +23648,7 @@
       <c r="B455" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C455" s="26" t="s">
+      <c r="C455" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D455" s="16" t="s">
@@ -23686,7 +23683,7 @@
       <c r="B456" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C456" s="26" t="s">
+      <c r="C456" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D456" s="16" t="s">
@@ -23721,7 +23718,7 @@
       <c r="B457" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C457" s="26" t="s">
+      <c r="C457" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D457" s="16" t="s">
@@ -23756,7 +23753,7 @@
       <c r="B458" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C458" s="26" t="s">
+      <c r="C458" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D458" s="16" t="s">
@@ -23791,7 +23788,7 @@
       <c r="B459" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C459" s="26" t="s">
+      <c r="C459" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D459" s="16" t="s">
@@ -23826,7 +23823,7 @@
       <c r="B460" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C460" s="26" t="s">
+      <c r="C460" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D460" s="16" t="s">
@@ -23861,7 +23858,7 @@
       <c r="B461" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C461" s="26" t="s">
+      <c r="C461" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D461" s="16" t="s">
@@ -23896,7 +23893,7 @@
       <c r="B462" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C462" s="26" t="s">
+      <c r="C462" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D462" s="16" t="s">
@@ -23931,7 +23928,7 @@
       <c r="B463" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C463" s="26" t="s">
+      <c r="C463" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D463" s="16" t="s">
@@ -23966,7 +23963,7 @@
       <c r="B464" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C464" s="26" t="s">
+      <c r="C464" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D464" s="16" t="s">
@@ -24001,7 +23998,7 @@
       <c r="B465" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C465" s="26" t="s">
+      <c r="C465" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D465" s="16" t="s">
@@ -24036,7 +24033,7 @@
       <c r="B466" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C466" s="26" t="s">
+      <c r="C466" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D466" s="16" t="s">
@@ -24071,7 +24068,7 @@
       <c r="B467" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C467" s="26" t="s">
+      <c r="C467" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D467" s="16" t="s">
@@ -24106,7 +24103,7 @@
       <c r="B468" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="C468" s="26" t="s">
+      <c r="C468" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D468" s="16" t="s">
@@ -24141,7 +24138,7 @@
       <c r="B469" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C469" s="26" t="s">
+      <c r="C469" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D469" s="16" t="s">
@@ -24176,7 +24173,7 @@
       <c r="B470" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C470" s="26" t="s">
+      <c r="C470" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D470" s="16" t="s">
@@ -24211,7 +24208,7 @@
       <c r="B471" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C471" s="26" t="s">
+      <c r="C471" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D471" s="16" t="s">
@@ -24246,7 +24243,7 @@
       <c r="B472" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C472" s="26" t="s">
+      <c r="C472" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D472" s="16" t="s">
@@ -24281,7 +24278,7 @@
       <c r="B473" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C473" s="26" t="s">
+      <c r="C473" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D473" s="16" t="s">
@@ -24316,7 +24313,7 @@
       <c r="B474" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C474" s="26" t="s">
+      <c r="C474" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D474" s="16" t="s">
@@ -24351,7 +24348,7 @@
       <c r="B475" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C475" s="26" t="s">
+      <c r="C475" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D475" s="16" t="s">
@@ -24386,7 +24383,7 @@
       <c r="B476" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C476" s="26" t="s">
+      <c r="C476" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D476" s="16" t="s">
@@ -24421,7 +24418,7 @@
       <c r="B477" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C477" s="26" t="s">
+      <c r="C477" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D477" s="16" t="s">
@@ -24456,7 +24453,7 @@
       <c r="B478" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C478" s="26" t="s">
+      <c r="C478" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D478" s="16" t="s">
@@ -24491,7 +24488,7 @@
       <c r="B479" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C479" s="26" t="s">
+      <c r="C479" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D479" s="16" t="s">
@@ -24526,7 +24523,7 @@
       <c r="B480" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C480" s="26" t="s">
+      <c r="C480" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D480" s="16" t="s">
@@ -24561,7 +24558,7 @@
       <c r="B481" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C481" s="26" t="s">
+      <c r="C481" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D481" s="16" t="s">
@@ -24596,7 +24593,7 @@
       <c r="B482" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C482" s="26" t="s">
+      <c r="C482" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D482" s="16" t="s">
@@ -24631,7 +24628,7 @@
       <c r="B483" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C483" s="26" t="s">
+      <c r="C483" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D483" s="16" t="s">
@@ -24666,7 +24663,7 @@
       <c r="B484" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C484" s="26" t="s">
+      <c r="C484" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D484" s="16" t="s">
@@ -24701,7 +24698,7 @@
       <c r="B485" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C485" s="26" t="s">
+      <c r="C485" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D485" s="16" t="s">
@@ -24736,7 +24733,7 @@
       <c r="B486" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C486" s="26" t="s">
+      <c r="C486" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D486" s="16" t="s">
@@ -24771,7 +24768,7 @@
       <c r="B487" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C487" s="26" t="s">
+      <c r="C487" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D487" s="16" t="s">
@@ -24806,7 +24803,7 @@
       <c r="B488" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C488" s="26" t="s">
+      <c r="C488" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D488" s="16" t="s">
@@ -24841,7 +24838,7 @@
       <c r="B489" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C489" s="26" t="s">
+      <c r="C489" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D489" s="16" t="s">
@@ -24876,7 +24873,7 @@
       <c r="B490" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C490" s="26" t="s">
+      <c r="C490" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D490" s="16" t="s">
@@ -24911,7 +24908,7 @@
       <c r="B491" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C491" s="26" t="s">
+      <c r="C491" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D491" s="16" t="s">
@@ -24946,7 +24943,7 @@
       <c r="B492" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C492" s="26" t="s">
+      <c r="C492" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D492" s="16" t="s">
@@ -24981,7 +24978,7 @@
       <c r="B493" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C493" s="26" t="s">
+      <c r="C493" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D493" s="16" t="s">
@@ -25016,7 +25013,7 @@
       <c r="B494" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C494" s="26" t="s">
+      <c r="C494" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D494" s="16" t="s">
@@ -25051,7 +25048,7 @@
       <c r="B495" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C495" s="26" t="s">
+      <c r="C495" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D495" s="16" t="s">
@@ -25086,7 +25083,7 @@
       <c r="B496" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C496" s="26" t="s">
+      <c r="C496" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D496" s="16" t="s">
@@ -25121,7 +25118,7 @@
       <c r="B497" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C497" s="26" t="s">
+      <c r="C497" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D497" s="16" t="s">
@@ -25156,7 +25153,7 @@
       <c r="B498" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C498" s="26" t="s">
+      <c r="C498" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D498" s="16" t="s">
@@ -25191,7 +25188,7 @@
       <c r="B499" s="16" t="s">
         <v>2107</v>
       </c>
-      <c r="C499" s="26" t="s">
+      <c r="C499" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D499" s="16" t="s">
@@ -25226,7 +25223,7 @@
       <c r="B500" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C500" s="26" t="s">
+      <c r="C500" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D500" s="16" t="s">
@@ -25261,7 +25258,7 @@
       <c r="B501" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C501" s="26" t="s">
+      <c r="C501" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D501" s="16" t="s">
@@ -25296,7 +25293,7 @@
       <c r="B502" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C502" s="26" t="s">
+      <c r="C502" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D502" s="16" t="s">
@@ -25331,7 +25328,7 @@
       <c r="B503" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C503" s="26" t="s">
+      <c r="C503" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D503" s="16" t="s">
@@ -25366,7 +25363,7 @@
       <c r="B504" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C504" s="26" t="s">
+      <c r="C504" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D504" s="16" t="s">
@@ -25401,7 +25398,7 @@
       <c r="B505" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C505" s="26" t="s">
+      <c r="C505" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D505" s="16" t="s">
@@ -25436,7 +25433,7 @@
       <c r="B506" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C506" s="26" t="s">
+      <c r="C506" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D506" s="16" t="s">
@@ -25471,7 +25468,7 @@
       <c r="B507" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C507" s="26" t="s">
+      <c r="C507" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D507" s="16" t="s">
@@ -25506,7 +25503,7 @@
       <c r="B508" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C508" s="26" t="s">
+      <c r="C508" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D508" s="16" t="s">
@@ -25541,7 +25538,7 @@
       <c r="B509" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C509" s="26" t="s">
+      <c r="C509" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D509" s="16" t="s">
@@ -25576,7 +25573,7 @@
       <c r="B510" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C510" s="26" t="s">
+      <c r="C510" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D510" s="16" t="s">
@@ -25611,7 +25608,7 @@
       <c r="B511" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C511" s="26" t="s">
+      <c r="C511" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D511" s="16" t="s">
@@ -25646,7 +25643,7 @@
       <c r="B512" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C512" s="26" t="s">
+      <c r="C512" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D512" s="16" t="s">
@@ -25681,7 +25678,7 @@
       <c r="B513" s="16" t="s">
         <v>2093</v>
       </c>
-      <c r="C513" s="26" t="s">
+      <c r="C513" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D513" s="16" t="s">
@@ -25716,7 +25713,7 @@
       <c r="B514" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C514" s="26" t="s">
+      <c r="C514" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D514" s="16" t="s">
@@ -25751,7 +25748,7 @@
       <c r="B515" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C515" s="26" t="s">
+      <c r="C515" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D515" s="16" t="s">
@@ -25786,7 +25783,7 @@
       <c r="B516" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C516" s="26" t="s">
+      <c r="C516" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D516" s="16" t="s">
@@ -25821,7 +25818,7 @@
       <c r="B517" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C517" s="26" t="s">
+      <c r="C517" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D517" s="16" t="s">
@@ -25856,7 +25853,7 @@
       <c r="B518" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C518" s="26" t="s">
+      <c r="C518" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D518" s="16" t="s">
@@ -25891,7 +25888,7 @@
       <c r="B519" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C519" s="26" t="s">
+      <c r="C519" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D519" s="16" t="s">
@@ -25926,7 +25923,7 @@
       <c r="B520" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C520" s="26" t="s">
+      <c r="C520" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D520" s="16" t="s">
@@ -25961,7 +25958,7 @@
       <c r="B521" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C521" s="26" t="s">
+      <c r="C521" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D521" s="16" t="s">
@@ -25996,7 +25993,7 @@
       <c r="B522" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C522" s="26" t="s">
+      <c r="C522" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D522" s="16" t="s">
@@ -26031,7 +26028,7 @@
       <c r="B523" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C523" s="26" t="s">
+      <c r="C523" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D523" s="16" t="s">
@@ -26066,7 +26063,7 @@
       <c r="B524" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C524" s="26" t="s">
+      <c r="C524" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D524" s="16" t="s">
@@ -26101,7 +26098,7 @@
       <c r="B525" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C525" s="26" t="s">
+      <c r="C525" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D525" s="16" t="s">
@@ -26136,7 +26133,7 @@
       <c r="B526" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C526" s="26" t="s">
+      <c r="C526" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D526" s="16" t="s">
@@ -26171,7 +26168,7 @@
       <c r="B527" s="16" t="s">
         <v>2094</v>
       </c>
-      <c r="C527" s="26" t="s">
+      <c r="C527" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D527" s="16" t="s">
@@ -26206,7 +26203,7 @@
       <c r="B528" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C528" s="26" t="s">
+      <c r="C528" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D528" s="16" t="s">
@@ -26241,7 +26238,7 @@
       <c r="B529" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C529" s="26" t="s">
+      <c r="C529" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D529" s="16" t="s">
@@ -26276,7 +26273,7 @@
       <c r="B530" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C530" s="26" t="s">
+      <c r="C530" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D530" s="16" t="s">
@@ -26311,7 +26308,7 @@
       <c r="B531" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C531" s="26" t="s">
+      <c r="C531" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D531" s="16" t="s">
@@ -26346,7 +26343,7 @@
       <c r="B532" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C532" s="26" t="s">
+      <c r="C532" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D532" s="16" t="s">
@@ -26381,7 +26378,7 @@
       <c r="B533" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C533" s="26" t="s">
+      <c r="C533" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D533" s="16" t="s">
@@ -26416,7 +26413,7 @@
       <c r="B534" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C534" s="26" t="s">
+      <c r="C534" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D534" s="16" t="s">
@@ -26451,7 +26448,7 @@
       <c r="B535" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C535" s="26" t="s">
+      <c r="C535" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D535" s="16" t="s">
@@ -26486,7 +26483,7 @@
       <c r="B536" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C536" s="26" t="s">
+      <c r="C536" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D536" s="16" t="s">
@@ -26521,7 +26518,7 @@
       <c r="B537" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C537" s="26" t="s">
+      <c r="C537" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D537" s="16" t="s">
@@ -26556,7 +26553,7 @@
       <c r="B538" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C538" s="26" t="s">
+      <c r="C538" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D538" s="16" t="s">
@@ -26591,7 +26588,7 @@
       <c r="B539" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C539" s="26" t="s">
+      <c r="C539" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D539" s="16" t="s">
@@ -26626,7 +26623,7 @@
       <c r="B540" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C540" s="26" t="s">
+      <c r="C540" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D540" s="16" t="s">
@@ -26661,7 +26658,7 @@
       <c r="B541" s="20" t="s">
         <v>2142</v>
       </c>
-      <c r="C541" s="26" t="s">
+      <c r="C541" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D541" s="16" t="s">
@@ -26696,7 +26693,7 @@
       <c r="B542" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C542" s="26" t="s">
+      <c r="C542" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D542" s="16" t="s">
@@ -26731,7 +26728,7 @@
       <c r="B543" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C543" s="26" t="s">
+      <c r="C543" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D543" s="16" t="s">
@@ -26766,7 +26763,7 @@
       <c r="B544" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C544" s="26" t="s">
+      <c r="C544" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D544" s="16" t="s">
@@ -26801,7 +26798,7 @@
       <c r="B545" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C545" s="26" t="s">
+      <c r="C545" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D545" s="16" t="s">
@@ -26836,7 +26833,7 @@
       <c r="B546" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C546" s="26" t="s">
+      <c r="C546" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D546" s="16" t="s">
@@ -26871,7 +26868,7 @@
       <c r="B547" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C547" s="26" t="s">
+      <c r="C547" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D547" s="16" t="s">
@@ -26906,7 +26903,7 @@
       <c r="B548" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C548" s="26" t="s">
+      <c r="C548" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D548" s="16" t="s">
@@ -26941,7 +26938,7 @@
       <c r="B549" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C549" s="26" t="s">
+      <c r="C549" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D549" s="16" t="s">
@@ -26976,7 +26973,7 @@
       <c r="B550" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C550" s="26" t="s">
+      <c r="C550" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D550" s="16" t="s">
@@ -27011,7 +27008,7 @@
       <c r="B551" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C551" s="26" t="s">
+      <c r="C551" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D551" s="16" t="s">
@@ -27046,7 +27043,7 @@
       <c r="B552" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C552" s="26" t="s">
+      <c r="C552" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D552" s="16" t="s">
@@ -27081,7 +27078,7 @@
       <c r="B553" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C553" s="26" t="s">
+      <c r="C553" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D553" s="16" t="s">
@@ -27116,7 +27113,7 @@
       <c r="B554" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C554" s="26" t="s">
+      <c r="C554" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D554" s="16" t="s">
@@ -27151,7 +27148,7 @@
       <c r="B555" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C555" s="26" t="s">
+      <c r="C555" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D555" s="16" t="s">
@@ -27186,7 +27183,7 @@
       <c r="B556" s="20" t="s">
         <v>2143</v>
       </c>
-      <c r="C556" s="26" t="s">
+      <c r="C556" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D556" s="16" t="s">
@@ -27221,7 +27218,7 @@
       <c r="B557" s="16" t="s">
         <v>2145</v>
       </c>
-      <c r="C557" s="26" t="s">
+      <c r="C557" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D557" s="16" t="s">
@@ -27249,14 +27246,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A558" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B558" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C558" s="26" t="s">
+      <c r="C558" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D558" s="16" t="s">
@@ -27284,14 +27281,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A559" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B559" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C559" s="26" t="s">
+      <c r="C559" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D559" s="16" t="s">
@@ -27319,14 +27316,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A560" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B560" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C560" s="26" t="s">
+      <c r="C560" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D560" s="16" t="s">
@@ -27354,14 +27351,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A561" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B561" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C561" s="26" t="s">
+      <c r="C561" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D561" s="16" t="s">
@@ -27389,14 +27386,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A562" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B562" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C562" s="26" t="s">
+      <c r="C562" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D562" s="16" t="s">
@@ -27424,14 +27421,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A563" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B563" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C563" s="26" t="s">
+      <c r="C563" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D563" s="16" t="s">
@@ -27459,14 +27456,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A564" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B564" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C564" s="26" t="s">
+      <c r="C564" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D564" s="16" t="s">
@@ -27494,14 +27491,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A565" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B565" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C565" s="26" t="s">
+      <c r="C565" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D565" s="16" t="s">
@@ -27529,14 +27526,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A566" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B566" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C566" s="26" t="s">
+      <c r="C566" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D566" s="16" t="s">
@@ -27564,14 +27561,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A567" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B567" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C567" s="26" t="s">
+      <c r="C567" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D567" s="16" t="s">
@@ -27599,14 +27596,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A568" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B568" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C568" s="26" t="s">
+      <c r="C568" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D568" s="16" t="s">
@@ -27634,14 +27631,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A569" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B569" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C569" s="26" t="s">
+      <c r="C569" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D569" s="16" t="s">
@@ -27669,14 +27666,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A570" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B570" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C570" s="26" t="s">
+      <c r="C570" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D570" s="16" t="s">
@@ -27704,14 +27701,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A571" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B571" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C571" s="26" t="s">
+      <c r="C571" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D571" s="16" t="s">
@@ -27739,14 +27736,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A572" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B572" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C572" s="26" t="s">
+      <c r="C572" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D572" s="16" t="s">
@@ -27774,14 +27771,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A573" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B573" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C573" s="26" t="s">
+      <c r="C573" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D573" s="16" t="s">
@@ -27809,14 +27806,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A574" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B574" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C574" s="26" t="s">
+      <c r="C574" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D574" s="16" t="s">
@@ -27844,14 +27841,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A575" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B575" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C575" s="26" t="s">
+      <c r="C575" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D575" s="16" t="s">
@@ -27879,14 +27876,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A576" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B576" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C576" s="26" t="s">
+      <c r="C576" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D576" s="16" t="s">
@@ -27914,14 +27911,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A577" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B577" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C577" s="26" t="s">
+      <c r="C577" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D577" s="16" t="s">
@@ -27949,14 +27946,14 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:11" ht="24.9" x14ac:dyDescent="0.35">
       <c r="A578" s="16" t="s">
         <v>1586</v>
       </c>
       <c r="B578" s="20" t="s">
         <v>2145</v>
       </c>
-      <c r="C578" s="26" t="s">
+      <c r="C578" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D578" s="16" t="s">
@@ -27991,7 +27988,7 @@
       <c r="B579" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C579" s="26" t="s">
+      <c r="C579" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D579" s="16" t="s">
@@ -28026,7 +28023,7 @@
       <c r="B580" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C580" s="26" t="s">
+      <c r="C580" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D580" s="16" t="s">
@@ -28047,7 +28044,7 @@
       <c r="I580" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="J580" s="17">
+      <c r="J580" s="18">
         <v>46157.733541666668</v>
       </c>
       <c r="K580" s="17" t="s">
@@ -28061,7 +28058,7 @@
       <c r="B581" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C581" s="26" t="s">
+      <c r="C581" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D581" s="16" t="s">
@@ -28082,7 +28079,7 @@
       <c r="I581" s="17" t="s">
         <v>2150</v>
       </c>
-      <c r="J581" s="17">
+      <c r="J581" s="18">
         <v>46084.496979166666</v>
       </c>
       <c r="K581" s="17" t="s">
@@ -28096,7 +28093,7 @@
       <c r="B582" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C582" s="26" t="s">
+      <c r="C582" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D582" s="16" t="s">
@@ -28117,7 +28114,7 @@
       <c r="I582" s="17" t="s">
         <v>2150</v>
       </c>
-      <c r="J582" s="17">
+      <c r="J582" s="18">
         <v>46160.616990740738</v>
       </c>
       <c r="K582" s="17" t="s">
@@ -28131,7 +28128,7 @@
       <c r="B583" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C583" s="26" t="s">
+      <c r="C583" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D583" s="16" t="s">
@@ -28152,7 +28149,7 @@
       <c r="I583" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="J583" s="17">
+      <c r="J583" s="18">
         <v>46052.359293981484</v>
       </c>
       <c r="K583" s="17" t="s">
@@ -28166,7 +28163,7 @@
       <c r="B584" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C584" s="26" t="s">
+      <c r="C584" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D584" s="16" t="s">
@@ -28187,7 +28184,7 @@
       <c r="I584" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="J584" s="17">
+      <c r="J584" s="18">
         <v>46114.367395833331</v>
       </c>
       <c r="K584" s="17" t="s">
@@ -28201,7 +28198,7 @@
       <c r="B585" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C585" s="26" t="s">
+      <c r="C585" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D585" s="16" t="s">
@@ -28222,7 +28219,7 @@
       <c r="I585" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J585" s="17" t="s">
+      <c r="J585" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K585" s="17" t="s">
@@ -28236,7 +28233,7 @@
       <c r="B586" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C586" s="26" t="s">
+      <c r="C586" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D586" s="16" t="s">
@@ -28257,7 +28254,7 @@
       <c r="I586" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="J586" s="17">
+      <c r="J586" s="18">
         <v>46119.745451388888</v>
       </c>
       <c r="K586" s="17" t="s">
@@ -28271,7 +28268,7 @@
       <c r="B587" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C587" s="26" t="s">
+      <c r="C587" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D587" s="16" t="s">
@@ -28292,7 +28289,7 @@
       <c r="I587" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J587" s="17" t="s">
+      <c r="J587" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K587" s="17" t="s">
@@ -28306,7 +28303,7 @@
       <c r="B588" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C588" s="26" t="s">
+      <c r="C588" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D588" s="16" t="s">
@@ -28327,7 +28324,7 @@
       <c r="I588" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J588" s="17" t="s">
+      <c r="J588" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K588" s="17" t="s">
@@ -28341,7 +28338,7 @@
       <c r="B589" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C589" s="26" t="s">
+      <c r="C589" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D589" s="16" t="s">
@@ -28362,7 +28359,7 @@
       <c r="I589" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J589" s="17" t="s">
+      <c r="J589" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K589" s="17" t="s">
@@ -28376,7 +28373,7 @@
       <c r="B590" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C590" s="26" t="s">
+      <c r="C590" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D590" s="16" t="s">
@@ -28397,7 +28394,7 @@
       <c r="I590" s="17" t="s">
         <v>2163</v>
       </c>
-      <c r="J590" s="17">
+      <c r="J590" s="18">
         <v>46031.514826388891</v>
       </c>
       <c r="K590" s="17" t="s">
@@ -28411,7 +28408,7 @@
       <c r="B591" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C591" s="26" t="s">
+      <c r="C591" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D591" s="16" t="s">
@@ -28432,7 +28429,7 @@
       <c r="I591" s="17" t="s">
         <v>2163</v>
       </c>
-      <c r="J591" s="17">
+      <c r="J591" s="18">
         <v>46031.515243055554</v>
       </c>
       <c r="K591" s="17" t="s">
@@ -28446,7 +28443,7 @@
       <c r="B592" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C592" s="26" t="s">
+      <c r="C592" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D592" s="16" t="s">
@@ -28467,7 +28464,7 @@
       <c r="I592" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="J592" s="17">
+      <c r="J592" s="18">
         <v>46085.041168981479</v>
       </c>
       <c r="K592" s="17" t="s">
@@ -28481,7 +28478,7 @@
       <c r="B593" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C593" s="26" t="s">
+      <c r="C593" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D593" s="16" t="s">
@@ -28502,7 +28499,7 @@
       <c r="I593" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="J593" s="17">
+      <c r="J593" s="18">
         <v>46085.040532407409</v>
       </c>
       <c r="K593" s="17" t="s">
@@ -28516,7 +28513,7 @@
       <c r="B594" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C594" s="26" t="s">
+      <c r="C594" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D594" s="16" t="s">
@@ -28537,7 +28534,7 @@
       <c r="I594" s="17" t="s">
         <v>2163</v>
       </c>
-      <c r="J594" s="17">
+      <c r="J594" s="18">
         <v>46031.514293981483</v>
       </c>
       <c r="K594" s="17" t="s">
@@ -28551,7 +28548,7 @@
       <c r="B595" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C595" s="26" t="s">
+      <c r="C595" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D595" s="16" t="s">
@@ -28572,7 +28569,7 @@
       <c r="I595" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J595" s="17" t="s">
+      <c r="J595" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K595" s="17" t="s">
@@ -28586,7 +28583,7 @@
       <c r="B596" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C596" s="26" t="s">
+      <c r="C596" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D596" s="16" t="s">
@@ -28607,7 +28604,7 @@
       <c r="I596" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J596" s="17" t="s">
+      <c r="J596" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K596" s="17" t="s">
@@ -28621,7 +28618,7 @@
       <c r="B597" s="20" t="s">
         <v>2146</v>
       </c>
-      <c r="C597" s="26" t="s">
+      <c r="C597" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D597" s="16" t="s">
@@ -28642,7 +28639,7 @@
       <c r="I597" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J597" s="17" t="s">
+      <c r="J597" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K597" s="17" t="s">
@@ -28656,7 +28653,7 @@
       <c r="B598" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C598" s="26" t="s">
+      <c r="C598" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D598" s="16" t="s">
@@ -28691,7 +28688,7 @@
       <c r="B599" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C599" s="26" t="s">
+      <c r="C599" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D599" s="16" t="s">
@@ -28726,7 +28723,7 @@
       <c r="B600" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C600" s="26" t="s">
+      <c r="C600" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D600" s="16" t="s">
@@ -28761,7 +28758,7 @@
       <c r="B601" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C601" s="26" t="s">
+      <c r="C601" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D601" s="16" t="s">
@@ -28782,7 +28779,7 @@
       <c r="I601" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J601" s="17" t="s">
+      <c r="J601" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K601" s="17" t="s">
@@ -28796,7 +28793,7 @@
       <c r="B602" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C602" s="26" t="s">
+      <c r="C602" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D602" s="16" t="s">
@@ -28817,7 +28814,7 @@
       <c r="I602" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J602" s="17" t="s">
+      <c r="J602" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K602" s="17" t="s">
@@ -28831,7 +28828,7 @@
       <c r="B603" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C603" s="26" t="s">
+      <c r="C603" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D603" s="16" t="s">
@@ -28866,7 +28863,7 @@
       <c r="B604" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C604" s="26" t="s">
+      <c r="C604" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D604" s="16" t="s">
@@ -28887,7 +28884,7 @@
       <c r="I604" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="J604" s="17" t="s">
+      <c r="J604" s="18" t="s">
         <v>59</v>
       </c>
       <c r="K604" s="17" t="s">
@@ -28901,7 +28898,7 @@
       <c r="B605" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C605" s="26" t="s">
+      <c r="C605" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D605" s="16" t="s">
@@ -28936,7 +28933,7 @@
       <c r="B606" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C606" s="26" t="s">
+      <c r="C606" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D606" s="16" t="s">
@@ -28971,7 +28968,7 @@
       <c r="B607" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C607" s="26" t="s">
+      <c r="C607" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D607" s="16" t="s">
@@ -29006,7 +29003,7 @@
       <c r="B608" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C608" s="26" t="s">
+      <c r="C608" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D608" s="16" t="s">
@@ -29041,7 +29038,7 @@
       <c r="B609" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C609" s="26" t="s">
+      <c r="C609" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D609" s="16" t="s">
@@ -29076,7 +29073,7 @@
       <c r="B610" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C610" s="26" t="s">
+      <c r="C610" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D610" s="16" t="s">
@@ -29111,7 +29108,7 @@
       <c r="B611" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C611" s="26" t="s">
+      <c r="C611" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D611" s="16" t="s">
@@ -29146,7 +29143,7 @@
       <c r="B612" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C612" s="26" t="s">
+      <c r="C612" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D612" s="16" t="s">
@@ -29181,7 +29178,7 @@
       <c r="B613" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="C613" s="26" t="s">
+      <c r="C613" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D613" s="16" t="s">
@@ -29216,7 +29213,7 @@
       <c r="B614" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C614" s="26" t="s">
+      <c r="C614" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D614" s="16" t="s">
@@ -29251,7 +29248,7 @@
       <c r="B615" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C615" s="26" t="s">
+      <c r="C615" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D615" s="16" t="s">
@@ -29286,7 +29283,7 @@
       <c r="B616" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C616" s="26" t="s">
+      <c r="C616" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D616" s="16" t="s">
@@ -29321,7 +29318,7 @@
       <c r="B617" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C617" s="26" t="s">
+      <c r="C617" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D617" s="16" t="s">
@@ -29356,7 +29353,7 @@
       <c r="B618" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C618" s="26" t="s">
+      <c r="C618" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D618" s="16" t="s">
@@ -29391,7 +29388,7 @@
       <c r="B619" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C619" s="26" t="s">
+      <c r="C619" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D619" s="16" t="s">
@@ -29426,7 +29423,7 @@
       <c r="B620" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C620" s="26" t="s">
+      <c r="C620" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D620" s="16" t="s">
@@ -29461,7 +29458,7 @@
       <c r="B621" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C621" s="26" t="s">
+      <c r="C621" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D621" s="16" t="s">
@@ -29496,7 +29493,7 @@
       <c r="B622" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C622" s="26" t="s">
+      <c r="C622" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D622" s="16" t="s">
@@ -29531,7 +29528,7 @@
       <c r="B623" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C623" s="26" t="s">
+      <c r="C623" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D623" s="16" t="s">
@@ -29566,7 +29563,7 @@
       <c r="B624" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C624" s="26" t="s">
+      <c r="C624" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D624" s="16" t="s">
@@ -29601,7 +29598,7 @@
       <c r="B625" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C625" s="26" t="s">
+      <c r="C625" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D625" s="16" t="s">
@@ -29636,7 +29633,7 @@
       <c r="B626" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C626" s="26" t="s">
+      <c r="C626" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D626" s="16" t="s">
@@ -29671,7 +29668,7 @@
       <c r="B627" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C627" s="26" t="s">
+      <c r="C627" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D627" s="16" t="s">
@@ -29706,7 +29703,7 @@
       <c r="B628" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C628" s="26" t="s">
+      <c r="C628" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D628" s="16" t="s">
@@ -29741,7 +29738,7 @@
       <c r="B629" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C629" s="26" t="s">
+      <c r="C629" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D629" s="16" t="s">
@@ -29776,7 +29773,7 @@
       <c r="B630" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="C630" s="26" t="s">
+      <c r="C630" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D630" s="16" t="s">
@@ -29811,7 +29808,7 @@
       <c r="B631" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C631" s="26" t="s">
+      <c r="C631" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D631" s="16" t="s">
@@ -29846,7 +29843,7 @@
       <c r="B632" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C632" s="26" t="s">
+      <c r="C632" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D632" s="16" t="s">
@@ -29881,7 +29878,7 @@
       <c r="B633" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C633" s="26" t="s">
+      <c r="C633" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D633" s="16" t="s">
@@ -29916,7 +29913,7 @@
       <c r="B634" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C634" s="26" t="s">
+      <c r="C634" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D634" s="16" t="s">
@@ -29951,7 +29948,7 @@
       <c r="B635" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C635" s="26" t="s">
+      <c r="C635" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D635" s="16" t="s">
@@ -29986,7 +29983,7 @@
       <c r="B636" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C636" s="26" t="s">
+      <c r="C636" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D636" s="16" t="s">
@@ -30021,7 +30018,7 @@
       <c r="B637" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C637" s="26" t="s">
+      <c r="C637" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D637" s="16" t="s">
@@ -30056,7 +30053,7 @@
       <c r="B638" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C638" s="26" t="s">
+      <c r="C638" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D638" s="16" t="s">
@@ -30091,7 +30088,7 @@
       <c r="B639" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C639" s="26" t="s">
+      <c r="C639" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D639" s="16" t="s">
@@ -30126,7 +30123,7 @@
       <c r="B640" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C640" s="26" t="s">
+      <c r="C640" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D640" s="16" t="s">
@@ -30161,7 +30158,7 @@
       <c r="B641" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C641" s="26" t="s">
+      <c r="C641" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D641" s="16" t="s">
@@ -30196,7 +30193,7 @@
       <c r="B642" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C642" s="26" t="s">
+      <c r="C642" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D642" s="16" t="s">
@@ -30231,7 +30228,7 @@
       <c r="B643" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C643" s="26" t="s">
+      <c r="C643" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D643" s="16" t="s">
@@ -30266,7 +30263,7 @@
       <c r="B644" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C644" s="26" t="s">
+      <c r="C644" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D644" s="16" t="s">
@@ -30301,7 +30298,7 @@
       <c r="B645" s="20" t="s">
         <v>2176</v>
       </c>
-      <c r="C645" s="26" t="s">
+      <c r="C645" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D645" s="16" t="s">
@@ -30336,7 +30333,7 @@
       <c r="B646" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C646" s="26" t="s">
+      <c r="C646" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D646" s="16" t="s">
@@ -30371,7 +30368,7 @@
       <c r="B647" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C647" s="26" t="s">
+      <c r="C647" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D647" s="16" t="s">
@@ -30406,7 +30403,7 @@
       <c r="B648" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C648" s="26" t="s">
+      <c r="C648" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D648" s="16" t="s">
@@ -30441,7 +30438,7 @@
       <c r="B649" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C649" s="26" t="s">
+      <c r="C649" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D649" s="16" t="s">
@@ -30476,7 +30473,7 @@
       <c r="B650" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C650" s="26" t="s">
+      <c r="C650" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D650" s="16" t="s">
@@ -30511,7 +30508,7 @@
       <c r="B651" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C651" s="26" t="s">
+      <c r="C651" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D651" s="16" t="s">
@@ -30546,7 +30543,7 @@
       <c r="B652" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C652" s="26" t="s">
+      <c r="C652" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D652" s="16" t="s">
@@ -30581,7 +30578,7 @@
       <c r="B653" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C653" s="26" t="s">
+      <c r="C653" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D653" s="16" t="s">
@@ -30616,7 +30613,7 @@
       <c r="B654" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C654" s="26" t="s">
+      <c r="C654" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D654" s="16" t="s">
@@ -30651,7 +30648,7 @@
       <c r="B655" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C655" s="26" t="s">
+      <c r="C655" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D655" s="16" t="s">
@@ -30686,7 +30683,7 @@
       <c r="B656" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C656" s="26" t="s">
+      <c r="C656" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D656" s="16" t="s">
@@ -30721,7 +30718,7 @@
       <c r="B657" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C657" s="26" t="s">
+      <c r="C657" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D657" s="16" t="s">
@@ -30756,7 +30753,7 @@
       <c r="B658" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C658" s="26" t="s">
+      <c r="C658" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D658" s="16" t="s">
@@ -30791,7 +30788,7 @@
       <c r="B659" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C659" s="26" t="s">
+      <c r="C659" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D659" s="16" t="s">
@@ -30826,7 +30823,7 @@
       <c r="B660" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C660" s="26" t="s">
+      <c r="C660" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D660" s="16" t="s">
@@ -30861,7 +30858,7 @@
       <c r="B661" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C661" s="26" t="s">
+      <c r="C661" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D661" s="16" t="s">
@@ -30896,7 +30893,7 @@
       <c r="B662" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="C662" s="26" t="s">
+      <c r="C662" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D662" s="16" t="s">
@@ -30931,7 +30928,7 @@
       <c r="B663" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C663" s="26" t="s">
+      <c r="C663" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D663" s="16" t="s">
@@ -30966,7 +30963,7 @@
       <c r="B664" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C664" s="26" t="s">
+      <c r="C664" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D664" s="16" t="s">
@@ -31001,7 +30998,7 @@
       <c r="B665" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C665" s="26" t="s">
+      <c r="C665" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D665" s="16" t="s">
@@ -31036,7 +31033,7 @@
       <c r="B666" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C666" s="26" t="s">
+      <c r="C666" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D666" s="16" t="s">
@@ -31071,7 +31068,7 @@
       <c r="B667" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C667" s="26" t="s">
+      <c r="C667" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D667" s="16" t="s">
@@ -31106,7 +31103,7 @@
       <c r="B668" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C668" s="26" t="s">
+      <c r="C668" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D668" s="16" t="s">
@@ -31141,7 +31138,7 @@
       <c r="B669" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C669" s="26" t="s">
+      <c r="C669" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D669" s="16" t="s">
@@ -31176,7 +31173,7 @@
       <c r="B670" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C670" s="26" t="s">
+      <c r="C670" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D670" s="16" t="s">
@@ -31211,7 +31208,7 @@
       <c r="B671" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C671" s="26" t="s">
+      <c r="C671" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D671" s="16" t="s">
@@ -31246,7 +31243,7 @@
       <c r="B672" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C672" s="26" t="s">
+      <c r="C672" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D672" s="16" t="s">
@@ -31281,7 +31278,7 @@
       <c r="B673" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C673" s="26" t="s">
+      <c r="C673" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D673" s="16" t="s">
@@ -31316,7 +31313,7 @@
       <c r="B674" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C674" s="26" t="s">
+      <c r="C674" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D674" s="16" t="s">
@@ -31351,7 +31348,7 @@
       <c r="B675" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C675" s="26" t="s">
+      <c r="C675" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D675" s="16" t="s">
@@ -31386,7 +31383,7 @@
       <c r="B676" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C676" s="26" t="s">
+      <c r="C676" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D676" s="16" t="s">
@@ -31421,7 +31418,7 @@
       <c r="B677" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C677" s="26" t="s">
+      <c r="C677" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D677" s="16" t="s">
@@ -31456,7 +31453,7 @@
       <c r="B678" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C678" s="26" t="s">
+      <c r="C678" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D678" s="16" t="s">
@@ -31491,7 +31488,7 @@
       <c r="B679" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C679" s="26" t="s">
+      <c r="C679" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D679" s="16" t="s">
@@ -31526,7 +31523,7 @@
       <c r="B680" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C680" s="26" t="s">
+      <c r="C680" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D680" s="16" t="s">
@@ -31561,7 +31558,7 @@
       <c r="B681" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C681" s="26" t="s">
+      <c r="C681" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D681" s="16" t="s">
@@ -31596,7 +31593,7 @@
       <c r="B682" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C682" s="26" t="s">
+      <c r="C682" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D682" s="16" t="s">
@@ -31631,7 +31628,7 @@
       <c r="B683" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C683" s="26" t="s">
+      <c r="C683" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D683" s="16" t="s">
@@ -31666,7 +31663,7 @@
       <c r="B684" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="C684" s="26" t="s">
+      <c r="C684" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D684" s="16" t="s">
@@ -31701,7 +31698,7 @@
       <c r="B685" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C685" s="26" t="s">
+      <c r="C685" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D685" s="16" t="s">
@@ -31736,7 +31733,7 @@
       <c r="B686" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C686" s="26" t="s">
+      <c r="C686" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D686" s="16" t="s">
@@ -31771,7 +31768,7 @@
       <c r="B687" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C687" s="26" t="s">
+      <c r="C687" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D687" s="16" t="s">
@@ -31806,7 +31803,7 @@
       <c r="B688" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C688" s="26" t="s">
+      <c r="C688" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D688" s="16" t="s">
@@ -31841,7 +31838,7 @@
       <c r="B689" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C689" s="26" t="s">
+      <c r="C689" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D689" s="16" t="s">
@@ -31876,7 +31873,7 @@
       <c r="B690" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C690" s="26" t="s">
+      <c r="C690" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D690" s="16" t="s">
@@ -31909,7 +31906,7 @@
       <c r="B691" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C691" s="26" t="s">
+      <c r="C691" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D691" s="16" t="s">
@@ -31944,7 +31941,7 @@
       <c r="B692" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C692" s="26" t="s">
+      <c r="C692" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D692" s="16" t="s">
@@ -31979,7 +31976,7 @@
       <c r="B693" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C693" s="26" t="s">
+      <c r="C693" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D693" s="16" t="s">
@@ -32012,7 +32009,7 @@
       <c r="B694" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C694" s="26" t="s">
+      <c r="C694" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D694" s="16" t="s">
@@ -32045,7 +32042,7 @@
       <c r="B695" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C695" s="26" t="s">
+      <c r="C695" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D695" s="16" t="s">
@@ -32078,7 +32075,7 @@
       <c r="B696" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C696" s="26" t="s">
+      <c r="C696" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D696" s="16" t="s">
@@ -32113,7 +32110,7 @@
       <c r="B697" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C697" s="26" t="s">
+      <c r="C697" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D697" s="16" t="s">
@@ -32148,7 +32145,7 @@
       <c r="B698" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C698" s="26" t="s">
+      <c r="C698" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D698" s="16" t="s">
@@ -32183,7 +32180,7 @@
       <c r="B699" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C699" s="26" t="s">
+      <c r="C699" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D699" s="16" t="s">
@@ -32218,7 +32215,7 @@
       <c r="B700" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C700" s="26" t="s">
+      <c r="C700" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D700" s="16" t="s">
@@ -32253,7 +32250,7 @@
       <c r="B701" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C701" s="26" t="s">
+      <c r="C701" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D701" s="16" t="s">
@@ -32288,7 +32285,7 @@
       <c r="B702" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C702" s="26" t="s">
+      <c r="C702" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D702" s="16" t="s">
@@ -32323,7 +32320,7 @@
       <c r="B703" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C703" s="26" t="s">
+      <c r="C703" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D703" s="16" t="s">
@@ -32358,7 +32355,7 @@
       <c r="B704" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C704" s="26" t="s">
+      <c r="C704" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D704" s="16" t="s">
@@ -32393,7 +32390,7 @@
       <c r="B705" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C705" s="26" t="s">
+      <c r="C705" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D705" s="16" t="s">
@@ -32428,7 +32425,7 @@
       <c r="B706" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C706" s="26" t="s">
+      <c r="C706" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D706" s="16" t="s">
@@ -32463,7 +32460,7 @@
       <c r="B707" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C707" s="26" t="s">
+      <c r="C707" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D707" s="16" t="s">
@@ -32498,7 +32495,7 @@
       <c r="B708" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C708" s="26" t="s">
+      <c r="C708" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D708" s="16" t="s">
@@ -32533,7 +32530,7 @@
       <c r="B709" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C709" s="26" t="s">
+      <c r="C709" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D709" s="16" t="s">
@@ -32568,7 +32565,7 @@
       <c r="B710" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C710" s="26" t="s">
+      <c r="C710" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D710" s="16" t="s">
@@ -32603,7 +32600,7 @@
       <c r="B711" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C711" s="26" t="s">
+      <c r="C711" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D711" s="16" t="s">
@@ -32638,7 +32635,7 @@
       <c r="B712" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C712" s="26" t="s">
+      <c r="C712" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D712" s="16" t="s">
@@ -32673,7 +32670,7 @@
       <c r="B713" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C713" s="26" t="s">
+      <c r="C713" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D713" s="16" t="s">
@@ -32708,7 +32705,7 @@
       <c r="B714" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C714" s="26" t="s">
+      <c r="C714" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D714" s="16" t="s">
@@ -32743,7 +32740,7 @@
       <c r="B715" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C715" s="26" t="s">
+      <c r="C715" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D715" s="16" t="s">
@@ -32778,7 +32775,7 @@
       <c r="B716" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C716" s="26" t="s">
+      <c r="C716" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D716" s="16" t="s">
@@ -32813,7 +32810,7 @@
       <c r="B717" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C717" s="26" t="s">
+      <c r="C717" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D717" s="16" t="s">
@@ -32848,7 +32845,7 @@
       <c r="B718" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C718" s="26" t="s">
+      <c r="C718" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D718" s="16" t="s">
@@ -32883,7 +32880,7 @@
       <c r="B719" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C719" s="26" t="s">
+      <c r="C719" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D719" s="16" t="s">
@@ -32918,7 +32915,7 @@
       <c r="B720" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C720" s="26" t="s">
+      <c r="C720" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D720" s="16" t="s">
@@ -32953,7 +32950,7 @@
       <c r="B721" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C721" s="26" t="s">
+      <c r="C721" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D721" s="16" t="s">
@@ -32988,7 +32985,7 @@
       <c r="B722" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C722" s="26" t="s">
+      <c r="C722" s="16" t="s">
         <v>14</v>
       </c>
       <c r="D722" s="16" t="s">
@@ -33023,7 +33020,7 @@
       <c r="B723" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C723" s="26" t="s">
+      <c r="C723" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D723" s="16" t="s">
@@ -33058,7 +33055,7 @@
       <c r="B724" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C724" s="26" t="s">
+      <c r="C724" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D724" s="16" t="s">
@@ -33093,7 +33090,7 @@
       <c r="B725" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C725" s="26" t="s">
+      <c r="C725" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D725" s="16" t="s">
@@ -33128,7 +33125,7 @@
       <c r="B726" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C726" s="26" t="s">
+      <c r="C726" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D726" s="16" t="s">
@@ -33163,7 +33160,7 @@
       <c r="B727" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C727" s="26" t="s">
+      <c r="C727" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D727" s="16" t="s">
@@ -33198,7 +33195,7 @@
       <c r="B728" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C728" s="26" t="s">
+      <c r="C728" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D728" s="16" t="s">
@@ -33233,7 +33230,7 @@
       <c r="B729" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C729" s="26" t="s">
+      <c r="C729" s="16" t="s">
         <v>2200</v>
       </c>
       <c r="D729" s="16" t="s">
@@ -33268,7 +33265,7 @@
       <c r="B730" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C730" s="26" t="s">
+      <c r="C730" s="16" t="s">
         <v>2083</v>
       </c>
       <c r="D730" s="16" t="s">
@@ -33303,7 +33300,7 @@
       <c r="B731" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C731" s="26" t="s">
+      <c r="C731" s="16" t="s">
         <v>37</v>
       </c>
       <c r="D731" s="16" t="s">
@@ -33338,7 +33335,7 @@
       <c r="B732" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C732" s="26" t="s">
+      <c r="C732" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D732" s="16" t="s">
@@ -33373,7 +33370,7 @@
       <c r="B733" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C733" s="26" t="s">
+      <c r="C733" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D733" s="16" t="s">
@@ -33408,7 +33405,7 @@
       <c r="B734" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C734" s="26" t="s">
+      <c r="C734" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D734" s="16" t="s">
@@ -33443,7 +33440,7 @@
       <c r="B735" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C735" s="26" t="s">
+      <c r="C735" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D735" s="16" t="s">
@@ -33478,7 +33475,7 @@
       <c r="B736" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C736" s="26" t="s">
+      <c r="C736" s="16" t="s">
         <v>58</v>
       </c>
       <c r="D736" s="16" t="s">
@@ -33513,7 +33510,7 @@
       <c r="B737" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C737" s="26" t="s">
+      <c r="C737" s="16" t="s">
         <v>60</v>
       </c>
       <c r="D737" s="16" t="s">
@@ -33548,7 +33545,7 @@
       <c r="B738" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C738" s="26" t="s">
+      <c r="C738" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D738" s="16" t="s">
@@ -33604,7 +33601,7 @@
       <c r="I739" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="J739" s="16">
+      <c r="J739" s="18">
         <v>45978.604930555557</v>
       </c>
       <c r="K739" s="18" t="s">
@@ -33639,7 +33636,7 @@
       <c r="I740" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J740" s="16">
+      <c r="J740" s="18">
         <v>45973.698194444441</v>
       </c>
       <c r="K740" s="18" t="s">
@@ -33674,7 +33671,7 @@
       <c r="I741" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J741" s="16">
+      <c r="J741" s="18">
         <v>46115.380358796298</v>
       </c>
       <c r="K741" s="18" t="s">
@@ -33709,7 +33706,7 @@
       <c r="I742" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J742" s="16">
+      <c r="J742" s="18">
         <v>45989.662638888891</v>
       </c>
       <c r="K742" s="18" t="s">
@@ -33744,7 +33741,7 @@
       <c r="I743" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J743" s="16">
+      <c r="J743" s="18">
         <v>46115.366863425923</v>
       </c>
       <c r="K743" s="18" t="s">
@@ -33779,7 +33776,7 @@
       <c r="I744" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J744" s="16">
+      <c r="J744" s="18">
         <v>46115.363576388889</v>
       </c>
       <c r="K744" s="18" t="s">
@@ -33814,7 +33811,7 @@
       <c r="I745" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J745" s="16">
+      <c r="J745" s="18">
         <v>46007.664872685185</v>
       </c>
       <c r="K745" s="18" t="s">
@@ -33849,7 +33846,7 @@
       <c r="I746" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J746" s="16">
+      <c r="J746" s="18">
         <v>46007.663831018515</v>
       </c>
       <c r="K746" s="18" t="s">
@@ -33884,7 +33881,7 @@
       <c r="I747" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J747" s="16">
+      <c r="J747" s="18">
         <v>46007.662754629629</v>
       </c>
       <c r="K747" s="18" t="s">
@@ -33919,7 +33916,7 @@
       <c r="I748" s="16" t="s">
         <v>2190</v>
       </c>
-      <c r="J748" s="16">
+      <c r="J748" s="18">
         <v>45989.733726851853</v>
       </c>
       <c r="K748" s="18" t="s">
@@ -33954,7 +33951,7 @@
       <c r="I749" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="J749" s="16">
+      <c r="J749" s="18">
         <v>45978.585486111115</v>
       </c>
       <c r="K749" s="18" t="s">
@@ -33989,7 +33986,7 @@
       <c r="I750" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="J750" s="16">
+      <c r="J750" s="18">
         <v>45985.405011574076</v>
       </c>
       <c r="K750" s="18" t="s">
